--- a/army_masterdoc.xlsx
+++ b/army_masterdoc.xlsx
@@ -93,7 +93,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -227,6 +227,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001A4A6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006A4A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7EDD6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A6A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6F7E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="005A2E6A"/>
       </patternFill>
     </fill>
@@ -237,22 +267,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="006A1A6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002E5C3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF6B35"/>
       </patternFill>
     </fill>
   </fills>
@@ -282,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -428,6 +458,42 @@
     <xf numFmtId="0" fontId="1" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -437,7 +503,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -449,26 +515,32 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -838,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1462,22 +1534,22 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Retreat System</t>
+          <t>Civ-Style Army Death</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>army.gd calculateAttackerResults / calculateDefenderResults</t>
+          <t>army.gd armyDestroyed signal, country.gd _on_army_destroyed()</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Retreat triggers at &lt; 25% manpower ratio. Sets inRetreat = true. deleteMode = true when manpower hits 0.</t>
+          <t>When manpowerInArmy ≤ 0, army emits signal armyDestroyed(self). country.gd connects handler in addArmy(): erases army from countryArmyList, nulls tile.stationedArmy, calls army.queue_free(). No retreat system — armies simply die at 0 manpower.</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>inRetreat flag is set but no retreat path execution logic is wired. deleteMode set but army removal from world tile not automated.</t>
+          <t>inRetreat and retreatTarget vars still declared but no longer emitted. May clean up later.</t>
         </is>
       </c>
     </row>
@@ -1610,9 +1682,9 @@
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -1622,22 +1694,22 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Terrain Combat Bonuses (36 new mods)</t>
+          <t>Terrain Combat Bonuses (36 commander mods)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>mil_mod.gd, unit.gd calculateMilMods()</t>
+          <t>mil_mod.gd, unit.gd calculateMilMods(), army.gd surveySelf()</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>All 36 new commander mil mods (Woodsman, Swamp Legs, Hill Runner, Marine, Entrenched, Guerrilla Tactics, etc.) are defined in mil_mod.gd with full descriptions. NONE have cases in calculateMilMods() yet — they are data-complete but effect-dead.</t>
+          <t>All 36 commander mil mods have cases in calculateMilMods(). surveySelf() sets unit.currentTerrain = inTile.terrain and unit.currentStorm before calling calculateMilMods(). Woodsman, Swamp Legs, Hill Runner, Street Tough, Farmhand, Guerrilla Tactics, Backcountry Rider, Frontier Marksman, Everglades Tracker, Bayou Warrior all apply terrain bonuses. Continental Line, Last Stand, Saber Drill, Marksman, Steady Line apply directly. Marine, Entrenched, Night Raider, Iron Wall etc. still flagged IDEA pending subsystems.</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Need: terrain check in calculateMilMods(); tile.terrain passed into army; Marine: navalTileNeighbors melee logic; Entrenched: stationary turn counter.</t>
+          <t>Marine: navalTileNeighbors melee logic still needed. Entrenched: stationary turn counter still needed.</t>
         </is>
       </c>
     </row>
@@ -2642,9 +2714,9 @@
       <c r="F66" s="7" t="inlineStr"/>
     </row>
     <row r="67" ht="44" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="B67" s="25" t="inlineStr">
@@ -2654,25 +2726,29 @@
       </c>
       <c r="C67" s="26" t="inlineStr">
         <is>
-          <t>Hurricane / Storm Events</t>
+          <t>Storm Event System</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>tile.gd is_hurricane_territory(), is_storm_prone()</t>
+          <t>tile.gd (storm vars), world.gd (_tick_storms, _spawn_storm, _spread_storm, _determine_storm_type)</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Helper functions defined. Tile winter eco modifier for hurricane zones set. No specific hurricane combat/movement events wired.</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr"/>
+          <t>Storms spawn each turn at 3% chance on a random tile. Storm type determined by tile.winterScore + terrain (Tornado in Farmlands/Foothills, Hurricane/Thunderstorm in tropics, Blizzard/Nor'easter in cold zones, Fog/Thunderstorm/Nor'easter in temperate). Storm spreads to all TileNeighbors; duration 2–6 turns, intensity 1–3. _tick_storms() decrements duration each turn and clears expired storms. tile.stormActive, stormType, stormDuration, stormIntensity, stormOriginId properties on Tile.</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Storm combat effects (morale, movement penalties, supply) are NOT yet applied. Only the 12 storm counter mods in calculateMilMods read currentStorm for bonuses.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="44" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="B68" s="25" t="inlineStr">
@@ -2682,17 +2758,17 @@
       </c>
       <c r="C68" s="26" t="inlineStr">
         <is>
-          <t>Weather Combat Effects</t>
+          <t>Storm Counter Mods (12 mods)</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>(design intent only)</t>
+          <t>mil_mod.gd, unit.gd calculateMilMods()</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>No combat stat penalties from weather. Rain/snow/fog could reduce ranged effectiveness or add to terrain mod costs. Storm Prone tiles could have randomized penalties.</t>
+          <t>12 storm counter mil mods: Fog-Born, Storm Rider, Thunder Proof, Blizzard March, Hurricane Eyes, Tornado Dancer, Nor'easter Veteran, Rain Reader, White Out Walker, Storm Chaser, Lightning Rod, Eye of the Storm. All have stormMod=true and stormType set. Direct stat bonuses read currentStorm in calculateMilMods(). Movement/immunity effects flagged IDEA pending army-level storm checks.</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -2894,9 +2970,9 @@
       </c>
     </row>
     <row r="77" ht="44" customHeight="1">
-      <c r="A77" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="B77" s="29" t="inlineStr">
@@ -2911,15 +2987,19 @@
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>mil_mod.gd</t>
+          <t>battle.gd _calculate_ranged_damage()</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Double Shot (T2): 'siege fires twice per round — second at 50% power'. Double Cannonade (T3): 'siege fires twice AND +3 attack on all shots'. No second-shot loop in battle.gd ranged calculation.</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr"/>
+          <t>Double Shot (T2): second volley at 50% power for all artillery units. Double Cannonade (T3): second volley at 100% power + 3 bonus per artillery unit. Detected via _army_has_siege_mod(). Second shot calculates against remaining shield after first shot, then adds to defenderManpowerLoss.</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Second shot only uses artillery units' ranged offence (not muskets/sabers).</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="44" customHeight="1">
       <c r="A78" s="13" t="inlineStr">
@@ -2954,32 +3034,160 @@
       </c>
     </row>
     <row r="79" ht="44" customHeight="1">
-      <c r="A79" s="14" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B79" s="29" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C79" s="30" t="inlineStr">
+        <is>
+          <t>Mythic Weapons (9 Easter Egg)</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>weapon.gd</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>9 Mythic-class weapons unlockable only via events: Baseball Bat, Trident, Mythic Atlatl, Sharps Carbine, Blackbeard's Pistols, Colt Revolver, Rocket Artillery, Trebuchet, Wright Flyer. All have Mythic-class embedded mods defined in mil_mod.gd. is_mythic() helper added to Weapon class. can_melee() excludes Rocket Artillery and Wright Flyer.</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Mythic mod effects partially stubbed (PirateVolley, CylinderFire, TrebuchetLaunch, etc. need battle.gd cases). RocketBarrage/AerialBombing tile effects not yet implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B80" s="29" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C80" s="30" t="inlineStr">
+        <is>
+          <t>Cultural / State-Specific Mods (12 mods)</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
+        <is>
+          <t>mil_mod.gd, governor.gd</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>12 state-exclusive cultural mods: Country Musician (TN), Virginia Gentry (VA), Minuteman's Pride (MA), Quaker Steel (PA), Georgia Peach (GA), Backcountry Rider (SC), Harbor Watch (NY), Chesapeake Sailor (MD), Frontier Marksman (KY), River Runner (OH), Everglades Tracker (FL), Bayou Warrior (LA). All have culturalMod=true and culturalState set. Stat bonuses apply via calculateMilMods(). Gate enforcement (only correct-state governors can have it) is handled at assignment time (event or archetype assignment — not auto-enforced in code).</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>No code auto-prevents wrong-state governors from having cultural mods. Must be assigned correctly at event/archetype assignment time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B81" s="29" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>Tool Mods (12 expanded civilian mods)</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>mil_mod.gd</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>12 new civilian tool mods: Cartographer, Herbalist, Engineer, Blacksmith, Physician, Merchant, Preacher, Architect, Hunter, Fisherman, Surveyor, Trapper. All have toolMod=true flag. Effects described in milModDescription. Added alongside existing civilian mods (Wooden Tools, Metal Tools, etc.).</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>All tool mod gameplay effects are IDEA tier — no per-turn hooks wired to any of them yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C82" s="30" t="inlineStr">
+        <is>
+          <t>New Uniforms: Tombstone Cap + Hardee Hat</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="inlineStr">
+        <is>
+          <t>armor.gd</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Tombstone Cap: Uniform class, M10/R20/S5, QuickDraw mod (+5 first ranged attack/battle). Hardee Hat: Uniform class, M15/R25/S10, HardeeDisc mod (+3 DEF/level adjacent friendly). Both mods defined in mil_mod.gd.</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>QuickDraw and HardeeDisc effects are FIRST DRAFT — mods defined but first-attack tracking and adjacent-unit checks not yet in battle.gd/army.gd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B83" s="29" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="C79" s="30" t="inlineStr">
+      <c r="C83" s="30" t="inlineStr">
         <is>
           <t>Supply Lines</t>
         </is>
       </c>
-      <c r="D79" s="29" t="inlineStr">
+      <c r="D83" s="29" t="inlineStr">
         <is>
           <t>(army cost vars hint at it)</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>armyFoodCost/armyWeaponsCost accumulated in surveySelf(). Country resources depleted by these costs is not fully automated per turn.</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2992,7 +3200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5268,7 +5476,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="48" t="inlineStr">
         <is>
-          <t>Armor MODS</t>
+          <t>Storm MODS</t>
         </is>
       </c>
       <c r="B66" s="48" t="inlineStr"/>
@@ -5281,331 +5489,1702 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>DrillFormation</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B67" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>Fog-Born</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E67" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fog</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Continental: bonus when adjacent to other Continental units</t>
-        </is>
-      </c>
-      <c r="G67" s="37" t="inlineStr">
-        <is>
-          <t>IDEA — declared on Continental armor, 'handled at army level', no army-level check</t>
+          <t>+5 attack per level in Fog storm tiles</t>
+        </is>
+      </c>
+      <c r="G67" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — stormMod flag + stormType set; calculateMilMods reads currentStorm</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>LineFormation</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B68" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C68" s="51" t="inlineStr">
+        <is>
+          <t>Storm Rider</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E68" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Redcoat: bonus to ranged when in line formation</t>
+          <t>Movement not reduced by any active storm</t>
         </is>
       </c>
       <c r="G68" s="37" t="inlineStr">
         <is>
-          <t>IDEA — declared on Redcoat armor, 'handled at army level', no army-level check</t>
+          <t>IDEA — movement exemption needs army-level storm check</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>Skirmish</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B69" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>Thunder Proof</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E69" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Thunderstorm</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Light Infantry: can move and fire same turn</t>
+          <t>Immune to Thunderstorm morale penalty</t>
         </is>
       </c>
       <c r="G69" s="37" t="inlineStr">
         <is>
-          <t>IDEA — declared on Light Infantry, 'handled at army level', no movement-fire logic</t>
+          <t>IDEA — morale immunity needs army-level check</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>ShockTroop</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B70" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C70" s="51" t="inlineStr">
+        <is>
+          <t>Blizzard March</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E70" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blizzard</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Heavy Infantry: bonus damage on first melee attack</t>
-        </is>
-      </c>
-      <c r="G70" s="42" t="inlineStr">
-        <is>
-          <t>FIRST PASS — declared 'handled in battle.gd first strike bonus'; no first-round check in battle.gd</t>
+          <t>No movement or supply penalty in Blizzard tiles</t>
+        </is>
+      </c>
+      <c r="G70" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — supply/movement exemption needs army-level check</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>MountedCharge</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B71" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C71" s="51" t="inlineStr">
+        <is>
+          <t>Hurricane Eyes</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E71" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hurricane</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Cavalry: amplifies saber charge damage by 20%</t>
-        </is>
-      </c>
-      <c r="G71" s="42" t="inlineStr">
-        <is>
-          <t>FIRST PASS — case in calculateMilMods() adds 20% to offScore IF saber; inverted disabled check prevents firing</t>
+          <t>+5 attack per level in Hurricane storm tiles</t>
+        </is>
+      </c>
+      <c r="G71" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — reads currentStorm in calculateMilMods</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>GunCrewEfficiency</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B72" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C72" s="51" t="inlineStr">
+        <is>
+          <t>Tornado Dancer</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E72" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Artillery Corps: reduces reload by 1 turn</t>
-        </is>
-      </c>
-      <c r="G72" s="47" t="inlineStr">
-        <is>
-          <t>FULL PASS — checked in unit.gd start_reload() directly by milModType string; bypasses disabled check bug</t>
+          <t>Army ignores Tornado scatter and manpower drain</t>
+        </is>
+      </c>
+      <c r="G72" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — Tornado scatter effect not yet implemented</t>
         </is>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>Uniform</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>MinutemanSpirit</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B73" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C73" s="51" t="inlineStr">
+        <is>
+          <t>Nor'easter Veteran</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>(armor mod)</t>
+          <t>commanderMod, stormMod</t>
         </is>
       </c>
       <c r="E73" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nor'easter</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Minuteman: bonus morale in home territory</t>
-        </is>
-      </c>
-      <c r="G73" s="37" t="inlineStr">
-        <is>
-          <t>IDEA — declared on Minuteman, never read anywhere</t>
+          <t>+3 defense per level in Nor'easter tiles</t>
+        </is>
+      </c>
+      <c r="G73" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — reads currentStorm in calculateMilMods</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="49" t="inlineStr">
         <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>Civilian</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>Translator</t>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B74" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Ranged</t>
+        </is>
+      </c>
+      <c r="C74" s="51" t="inlineStr">
+        <is>
+          <t>Rain Reader</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>civilianMod</t>
+          <t>rangedMod, stormMod</t>
         </is>
       </c>
       <c r="E74" s="33" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Thunderstorm</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Enable reading of ancient writings</t>
-        </is>
-      </c>
-      <c r="G74" s="50" t="inlineStr">
-        <is>
-          <t>CIVILIAN — not a combat mod</t>
+          <t>+3 ranged attack per level during Thunderstorm</t>
+        </is>
+      </c>
+      <c r="G74" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — reads currentStorm in calculateMilMods</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="49" t="inlineStr">
         <is>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B75" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Infantry</t>
+        </is>
+      </c>
+      <c r="C75" s="51" t="inlineStr">
+        <is>
+          <t>White Out Walker</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>infantryMod, stormMod</t>
+        </is>
+      </c>
+      <c r="E75" s="33" t="inlineStr">
+        <is>
+          <t>Blizzard</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>+3 attack per level during Blizzard</t>
+        </is>
+      </c>
+      <c r="G75" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — reads currentStorm in calculateMilMods</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="49" t="inlineStr">
+        <is>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B76" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C76" s="51" t="inlineStr">
+        <is>
+          <t>Storm Chaser</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, stormMod</t>
+        </is>
+      </c>
+      <c r="E76" s="33" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>+1 movement point in any active storm tile</t>
+        </is>
+      </c>
+      <c r="G76" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — movement bonus needs army-level check</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="49" t="inlineStr">
+        <is>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B77" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Siege</t>
+        </is>
+      </c>
+      <c r="C77" s="51" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>siegeMod, stormMod</t>
+        </is>
+      </c>
+      <c r="E77" s="33" t="inlineStr">
+        <is>
+          <t>Thunderstorm</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Artillery units ignore storm ranged accuracy penalty</t>
+        </is>
+      </c>
+      <c r="G77" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — storm accuracy penalty not yet implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="49" t="inlineStr">
+        <is>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B78" s="50" t="inlineStr">
+        <is>
+          <t>Storm/Commander</t>
+        </is>
+      </c>
+      <c r="C78" s="51" t="inlineStr">
+        <is>
+          <t>Eye of the Storm</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, stormMod</t>
+        </is>
+      </c>
+      <c r="E78" s="33" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>+4 attack +4 defense per level while storm is active</t>
+        </is>
+      </c>
+      <c r="G78" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — reads currentStorm != '' in calculateMilMods</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="52" t="inlineStr">
+        <is>
+          <t>Cultural MODS</t>
+        </is>
+      </c>
+      <c r="B79" s="52" t="inlineStr"/>
+      <c r="C79" s="52" t="inlineStr"/>
+      <c r="D79" s="52" t="inlineStr"/>
+      <c r="E79" s="52" t="inlineStr"/>
+      <c r="F79" s="52" t="inlineStr"/>
+      <c r="G79" s="52" t="inlineStr"/>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B80" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/TN</t>
+        </is>
+      </c>
+      <c r="C80" s="55" t="inlineStr">
+        <is>
+          <t>Country Musician</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E80" s="33" t="inlineStr">
+        <is>
+          <t>TN only</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>+3 morale; +2 ATK/level in Farmlands. Tennessee governors only.</t>
+        </is>
+      </c>
+      <c r="G80" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — culturalState='TN'; terrain check in calculateMilMods</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B81" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/VA</t>
+        </is>
+      </c>
+      <c r="C81" s="55" t="inlineStr">
+        <is>
+          <t>Virginia Gentry</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E81" s="33" t="inlineStr">
+        <is>
+          <t>VA only</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>+3 ranged defense per level. Virginia governors only.</t>
+        </is>
+      </c>
+      <c r="G81" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — culturalState='VA'; calculateMilMods applies ranged def bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B82" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/MA</t>
+        </is>
+      </c>
+      <c r="C82" s="55" t="inlineStr">
+        <is>
+          <t>Minuteman's Pride</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E82" s="33" t="inlineStr">
+        <is>
+          <t>MA only</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>+5 ATK/level first 3 battle rounds. Massachusetts governors only.</t>
+        </is>
+      </c>
+      <c r="G82" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — first-round tracking not yet in battle.gd</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B83" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/PA</t>
+        </is>
+      </c>
+      <c r="C83" s="55" t="inlineStr">
+        <is>
+          <t>Quaker Steel</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E83" s="33" t="inlineStr">
+        <is>
+          <t>PA only</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>+2 DEF −1 ATK per level. Pennsylvania governors only.</t>
+        </is>
+      </c>
+      <c r="G83" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — calculateMilMods applies both bonuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B84" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/GA</t>
+        </is>
+      </c>
+      <c r="C84" s="55" t="inlineStr">
+        <is>
+          <t>Georgia Peach</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>infantryMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E84" s="33" t="inlineStr">
+        <is>
+          <t>GA only</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>+3 food efficiency; +1 ranged/level. Georgia governors only.</t>
+        </is>
+      </c>
+      <c r="G84" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — ranged bonus in calculateMilMods; food handled separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B85" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/SC</t>
+        </is>
+      </c>
+      <c r="C85" s="55" t="inlineStr">
+        <is>
+          <t>Backcountry Rider</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>infantryMod, terrainMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E85" s="33" t="inlineStr">
+        <is>
+          <t>SC only + Woods</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>+4 ATK/level in Woods. Carolina governors only.</t>
+        </is>
+      </c>
+      <c r="G85" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — terrain + cultural flags; calculateMilMods checks currentTerrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/NY</t>
+        </is>
+      </c>
+      <c r="C86" s="55" t="inlineStr">
+        <is>
+          <t>Harbor Watch</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, marineMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>NY only</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>+3 ATK/level near naval tiles. New York governors only.</t>
+        </is>
+      </c>
+      <c r="G86" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — near-naval check not in calculateMilMods yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B87" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/MD</t>
+        </is>
+      </c>
+      <c r="C87" s="55" t="inlineStr">
+        <is>
+          <t>Chesapeake Sailor</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, marineMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E87" s="33" t="inlineStr">
+        <is>
+          <t>MD only</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>+2 melee/level + Marine ability. Maryland governors only.</t>
+        </is>
+      </c>
+      <c r="G87" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — melee bonus in calculateMilMods; Marine handled at army level</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B88" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/KY</t>
+        </is>
+      </c>
+      <c r="C88" s="55" t="inlineStr">
+        <is>
+          <t>Frontier Marksman</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>rangedMod, terrainMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E88" s="33" t="inlineStr">
+        <is>
+          <t>KY only + Foothills</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>+4 ranged/level in Foothills. Kentucky governors only.</t>
+        </is>
+      </c>
+      <c r="G88" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — terrain + cultural flags; calculateMilMods checks currentTerrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B89" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/OH</t>
+        </is>
+      </c>
+      <c r="C89" s="55" t="inlineStr">
+        <is>
+          <t>River Runner</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E89" s="33" t="inlineStr">
+        <is>
+          <t>OH only</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>+2 movement; +2 ATK near water. Ohio governors only.</t>
+        </is>
+      </c>
+      <c r="G89" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — movement bonus and near-water check not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B90" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/FL</t>
+        </is>
+      </c>
+      <c r="C90" s="55" t="inlineStr">
+        <is>
+          <t>Everglades Tracker</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>infantryMod, terrainMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E90" s="33" t="inlineStr">
+        <is>
+          <t>FL only + Wetlands</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>+4 ATK+DEF/level in Wetlands. Florida governors only.</t>
+        </is>
+      </c>
+      <c r="G90" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — terrain check in calculateMilMods</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="53" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+      <c r="B91" s="54" t="inlineStr">
+        <is>
+          <t>Cultural/LA</t>
+        </is>
+      </c>
+      <c r="C91" s="55" t="inlineStr">
+        <is>
+          <t>Bayou Warrior</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>infantryMod, terrainMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E91" s="33" t="inlineStr">
+        <is>
+          <t>LA only + Wetlands</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>+5 ATK/level in Wetlands. Louisiana governors only.</t>
+        </is>
+      </c>
+      <c r="G91" s="34" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT — terrain check in calculateMilMods</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="56" t="inlineStr">
+        <is>
+          <t>Tool MODS</t>
+        </is>
+      </c>
+      <c r="B92" s="56" t="inlineStr"/>
+      <c r="C92" s="56" t="inlineStr"/>
+      <c r="D92" s="56" t="inlineStr"/>
+      <c r="E92" s="56" t="inlineStr"/>
+      <c r="F92" s="56" t="inlineStr"/>
+      <c r="G92" s="56" t="inlineStr"/>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B93" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C93" s="59" t="inlineStr">
+        <is>
+          <t>Cartographer</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E93" s="33" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Maps explored tiles, revealing terrain bonuses and hidden resources.</t>
+        </is>
+      </c>
+      <c r="G93" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — reveal logic not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B94" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C94" s="59" t="inlineStr">
+        <is>
+          <t>Herbalist</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E94" s="33" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>+5 manpower per turn in tile.</t>
+        </is>
+      </c>
+      <c r="G94" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — per-turn heal not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B95" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C95" s="59" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E95" s="33" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Builds roads and improves structures faster.</t>
+        </is>
+      </c>
+      <c r="G95" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — build speed modifier not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B96" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C96" s="59" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E96" s="33" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Reduces weapon upkeep by 1/level/turn for stationed armies.</t>
+        </is>
+      </c>
+      <c r="G96" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — weapon cost reduction not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B97" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C97" s="59" t="inlineStr">
+        <is>
+          <t>Physician</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E97" s="33" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>+10 manpower per turn to armies in tile.</t>
+        </is>
+      </c>
+      <c r="G97" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — army heal not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B98" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C98" s="59" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E98" s="33" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>+3 gold per turn.</t>
+        </is>
+      </c>
+      <c r="G98" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — gold generation not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B99" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C99" s="59" t="inlineStr">
+        <is>
+          <t>Preacher</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E99" s="33" t="inlineStr">
+        <is>
+          <t>Influence</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>+5 loyalty/turn for tile governor.</t>
+        </is>
+      </c>
+      <c r="G99" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — loyalty tick not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B100" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C100" s="59" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E100" s="33" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Reduces building costs by 15%.</t>
+        </is>
+      </c>
+      <c r="G100" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — cost reduction not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B101" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C101" s="59" t="inlineStr">
+        <is>
+          <t>Hunter</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E101" s="33" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>+5 food per turn.</t>
+        </is>
+      </c>
+      <c r="G101" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — food generation not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B102" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C102" s="59" t="inlineStr">
+        <is>
+          <t>Fisherman</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E102" s="33" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>+3 food per turn near water tiles.</t>
+        </is>
+      </c>
+      <c r="G102" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — water-adjacency food not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B103" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C103" s="59" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E103" s="33" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Reveals terrain bonuses of adjacent tiles.</t>
+        </is>
+      </c>
+      <c r="G103" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — reveal logic not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="57" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B104" s="58" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C104" s="59" t="inlineStr">
+        <is>
+          <t>Trapper</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E104" s="33" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>+2 food +1 trade per turn.</t>
+        </is>
+      </c>
+      <c r="G104" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — trade/food generation not yet wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="60" t="inlineStr">
+        <is>
+          <t>Armor MODS</t>
+        </is>
+      </c>
+      <c r="B105" s="60" t="inlineStr"/>
+      <c r="C105" s="60" t="inlineStr"/>
+      <c r="D105" s="60" t="inlineStr"/>
+      <c r="E105" s="60" t="inlineStr"/>
+      <c r="F105" s="60" t="inlineStr"/>
+      <c r="G105" s="60" t="inlineStr"/>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="A106" s="61" t="inlineStr">
+        <is>
           <t>Armor</t>
         </is>
       </c>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>DrillFormation</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E106" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Continental: bonus when adjacent to other Continental units</t>
+        </is>
+      </c>
+      <c r="G106" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — declared on Continental armor, 'handled at army level', no army-level check</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="A107" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>LineFormation</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E107" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Redcoat: bonus to ranged when in line formation</t>
+        </is>
+      </c>
+      <c r="G107" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — declared on Redcoat armor, 'handled at army level', no army-level check</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="A108" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>Skirmish</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E108" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Light Infantry: can move and fire same turn</t>
+        </is>
+      </c>
+      <c r="G108" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — declared on Light Infantry, 'handled at army level', no movement-fire logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>ShockTroop</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E109" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Heavy Infantry: bonus damage on first melee attack</t>
+        </is>
+      </c>
+      <c r="G109" s="42" t="inlineStr">
+        <is>
+          <t>FIRST PASS — declared 'handled in battle.gd first strike bonus'; no first-round check in battle.gd</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>MountedCharge</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E110" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Cavalry: amplifies saber charge damage by 20%</t>
+        </is>
+      </c>
+      <c r="G110" s="42" t="inlineStr">
+        <is>
+          <t>FIRST PASS — case in calculateMilMods() adds 20% to offScore IF saber; inverted disabled check prevents firing</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>GunCrewEfficiency</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E111" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>Artillery Corps: reduces reload by 1 turn</t>
+        </is>
+      </c>
+      <c r="G111" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — checked in unit.gd start_reload() directly by milModType string; bypasses disabled check bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>MinutemanSpirit</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>(armor mod)</t>
+        </is>
+      </c>
+      <c r="E112" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Minuteman: bonus morale in home territory</t>
+        </is>
+      </c>
+      <c r="G112" s="37" t="inlineStr">
+        <is>
+          <t>IDEA — declared on Minuteman, never read anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
         <is>
           <t>Civilian</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C113" s="18" t="inlineStr">
+        <is>
+          <t>Translator</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod</t>
+        </is>
+      </c>
+      <c r="E113" s="33" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Enable reading of ancient writings</t>
+        </is>
+      </c>
+      <c r="G113" s="62" t="inlineStr">
+        <is>
+          <t>CIVILIAN — not a combat mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="A114" s="61" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>Civilian</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
         <is>
           <t>Seeder</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>civilianMod</t>
         </is>
       </c>
-      <c r="E75" s="33" t="inlineStr">
+      <c r="E114" s="33" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>Change agricultural output of tile</t>
         </is>
       </c>
-      <c r="G75" s="50" t="inlineStr">
+      <c r="G114" s="62" t="inlineStr">
         <is>
           <t>CIVILIAN — not a combat mod</t>
         </is>
@@ -5622,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5730,42 +7309,42 @@
           <t>Cutlass</t>
         </is>
       </c>
-      <c r="C3" s="51" t="inlineStr">
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" s="51" t="inlineStr">
+      <c r="D3" s="63" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" s="51" t="inlineStr">
+      <c r="E3" s="63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="51" t="inlineStr">
+      <c r="F3" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" s="51" t="inlineStr">
+      <c r="G3" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="51" t="inlineStr">
+      <c r="H3" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I3" s="51" t="inlineStr">
+      <c r="I3" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="51" t="inlineStr">
+      <c r="J3" s="63" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -5792,42 +7371,42 @@
           <t>Cavalry Saber</t>
         </is>
       </c>
-      <c r="C4" s="51" t="inlineStr">
+      <c r="C4" s="63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="51" t="inlineStr">
+      <c r="D4" s="63" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr">
+      <c r="E4" s="63" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="51" t="inlineStr">
+      <c r="F4" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr">
+      <c r="G4" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="51" t="inlineStr">
+      <c r="H4" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="51" t="inlineStr">
+      <c r="I4" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="J4" s="63" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -5854,42 +7433,42 @@
           <t>Light Saber</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="63" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="51" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="H5" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="51" t="inlineStr">
+      <c r="I5" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="51" t="inlineStr">
+      <c r="J5" s="63" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -5916,42 +7495,42 @@
           <t>Heavy Saber</t>
         </is>
       </c>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="63" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E6" s="51" t="inlineStr">
+      <c r="E6" s="63" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F6" s="51" t="inlineStr">
+      <c r="F6" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="51" t="inlineStr">
+      <c r="G6" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" s="51" t="inlineStr">
+      <c r="H6" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I6" s="51" t="inlineStr">
+      <c r="I6" s="63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J6" s="51" t="inlineStr">
+      <c r="J6" s="63" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -5968,22 +7547,22 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>Musket CLASS</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr"/>
-      <c r="C7" s="52" t="inlineStr"/>
-      <c r="D7" s="52" t="inlineStr"/>
-      <c r="E7" s="52" t="inlineStr"/>
-      <c r="F7" s="52" t="inlineStr"/>
-      <c r="G7" s="52" t="inlineStr"/>
-      <c r="H7" s="52" t="inlineStr"/>
-      <c r="I7" s="52" t="inlineStr"/>
-      <c r="J7" s="52" t="inlineStr"/>
-      <c r="K7" s="52" t="inlineStr"/>
-      <c r="L7" s="52" t="inlineStr"/>
+      <c r="B7" s="64" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="64" t="inlineStr"/>
+      <c r="G7" s="64" t="inlineStr"/>
+      <c r="H7" s="64" t="inlineStr"/>
+      <c r="I7" s="64" t="inlineStr"/>
+      <c r="J7" s="64" t="inlineStr"/>
+      <c r="K7" s="64" t="inlineStr"/>
+      <c r="L7" s="64" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
@@ -5996,42 +7575,42 @@
           <t>Flintlock</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F8" s="53" t="inlineStr">
+      <c r="F8" s="65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G8" s="53" t="inlineStr">
+      <c r="G8" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H8" s="53" t="inlineStr">
+      <c r="H8" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="I8" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J8" s="53" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6058,42 +7637,42 @@
           <t>Brown Bess</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" s="53" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F9" s="53" t="inlineStr">
+      <c r="F9" s="65" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" s="53" t="inlineStr">
+      <c r="G9" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="H9" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" s="53" t="inlineStr">
+      <c r="I9" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J9" s="53" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6120,42 +7699,42 @@
           <t>Percussion Cap</t>
         </is>
       </c>
-      <c r="C10" s="53" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="D10" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E10" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="53" t="inlineStr">
+      <c r="F10" s="65" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G10" s="53" t="inlineStr">
+      <c r="G10" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="H10" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="I10" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6182,42 +7761,42 @@
           <t>Lever Repeater</t>
         </is>
       </c>
-      <c r="C11" s="53" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="65" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E11" s="53" t="inlineStr">
+      <c r="E11" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F11" s="53" t="inlineStr">
+      <c r="F11" s="65" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G11" s="53" t="inlineStr">
+      <c r="G11" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H11" s="53" t="inlineStr">
+      <c r="H11" s="65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I11" s="53" t="inlineStr">
+      <c r="I11" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J11" s="53" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6262,42 +7841,42 @@
           <t>Falconet</t>
         </is>
       </c>
-      <c r="C13" s="54" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="54" t="inlineStr">
+      <c r="E13" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="54" t="inlineStr">
+      <c r="F13" s="66" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G13" s="54" t="inlineStr">
+      <c r="G13" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H13" s="54" t="inlineStr">
+      <c r="H13" s="66" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="I13" s="66" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J13" s="54" t="inlineStr">
+      <c r="J13" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6324,42 +7903,42 @@
           <t>Field Gun</t>
         </is>
       </c>
-      <c r="C14" s="54" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="54" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="54" t="inlineStr">
+      <c r="E14" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="54" t="inlineStr">
+      <c r="F14" s="66" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G14" s="54" t="inlineStr">
+      <c r="G14" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="54" t="inlineStr">
+      <c r="H14" s="66" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I14" s="54" t="inlineStr">
+      <c r="I14" s="66" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J14" s="54" t="inlineStr">
+      <c r="J14" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6386,42 +7965,42 @@
           <t>Howitzer</t>
         </is>
       </c>
-      <c r="C15" s="54" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D15" s="54" t="inlineStr">
+      <c r="D15" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E15" s="54" t="inlineStr">
+      <c r="E15" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="54" t="inlineStr">
+      <c r="F15" s="66" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G15" s="54" t="inlineStr">
+      <c r="G15" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H15" s="54" t="inlineStr">
+      <c r="H15" s="66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="I15" s="66" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="J15" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6448,42 +8027,42 @@
           <t>Mortar</t>
         </is>
       </c>
-      <c r="C16" s="54" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="54" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="54" t="inlineStr">
+      <c r="E16" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="54" t="inlineStr">
+      <c r="F16" s="66" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G16" s="54" t="inlineStr">
+      <c r="G16" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H16" s="54" t="inlineStr">
+      <c r="H16" s="66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="54" t="inlineStr">
+      <c r="I16" s="66" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J16" s="54" t="inlineStr">
+      <c r="J16" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6528,42 +8107,42 @@
           <t>Atlatl</t>
         </is>
       </c>
-      <c r="C18" s="55" t="inlineStr">
+      <c r="C18" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E18" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="55" t="inlineStr">
+      <c r="F18" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G18" s="55" t="inlineStr">
+      <c r="G18" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H18" s="55" t="inlineStr">
+      <c r="H18" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I18" s="55" t="inlineStr">
+      <c r="I18" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J18" s="55" t="inlineStr">
+      <c r="J18" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6590,42 +8169,42 @@
           <t>Club</t>
         </is>
       </c>
-      <c r="C19" s="55" t="inlineStr">
+      <c r="C19" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="55" t="inlineStr">
+      <c r="D19" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="55" t="inlineStr">
+      <c r="E19" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="55" t="inlineStr">
+      <c r="F19" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G19" s="55" t="inlineStr">
+      <c r="G19" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H19" s="55" t="inlineStr">
+      <c r="H19" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I19" s="55" t="inlineStr">
+      <c r="I19" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J19" s="55" t="inlineStr">
+      <c r="J19" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6652,42 +8231,42 @@
           <t>Double Axe</t>
         </is>
       </c>
-      <c r="C20" s="55" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="55" t="inlineStr">
+      <c r="D20" s="67" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E20" s="55" t="inlineStr">
+      <c r="E20" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="55" t="inlineStr">
+      <c r="F20" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="55" t="inlineStr">
+      <c r="G20" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H20" s="55" t="inlineStr">
+      <c r="H20" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I20" s="55" t="inlineStr">
+      <c r="I20" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J20" s="55" t="inlineStr">
+      <c r="J20" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6714,42 +8293,42 @@
           <t>Flail</t>
         </is>
       </c>
-      <c r="C21" s="55" t="inlineStr">
+      <c r="C21" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E21" s="55" t="inlineStr">
+      <c r="E21" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F21" s="55" t="inlineStr">
+      <c r="F21" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" s="55" t="inlineStr">
+      <c r="G21" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" s="55" t="inlineStr">
+      <c r="H21" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I21" s="55" t="inlineStr">
+      <c r="I21" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J21" s="55" t="inlineStr">
+      <c r="J21" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6776,42 +8355,42 @@
           <t>Longsword</t>
         </is>
       </c>
-      <c r="C22" s="55" t="inlineStr">
+      <c r="C22" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="67" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="55" t="inlineStr">
+      <c r="E22" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="55" t="inlineStr">
+      <c r="F22" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="55" t="inlineStr">
+      <c r="G22" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H22" s="55" t="inlineStr">
+      <c r="H22" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I22" s="55" t="inlineStr">
+      <c r="I22" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" s="55" t="inlineStr">
+      <c r="J22" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6838,42 +8417,42 @@
           <t>Mace</t>
         </is>
       </c>
-      <c r="C23" s="55" t="inlineStr">
+      <c r="C23" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E23" s="55" t="inlineStr">
+      <c r="E23" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F23" s="55" t="inlineStr">
+      <c r="F23" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="55" t="inlineStr">
+      <c r="G23" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H23" s="55" t="inlineStr">
+      <c r="H23" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I23" s="55" t="inlineStr">
+      <c r="I23" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J23" s="55" t="inlineStr">
+      <c r="J23" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6900,42 +8479,42 @@
           <t>Machete</t>
         </is>
       </c>
-      <c r="C24" s="55" t="inlineStr">
+      <c r="C24" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E24" s="55" t="inlineStr">
+      <c r="E24" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="55" t="inlineStr">
+      <c r="F24" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="55" t="inlineStr">
+      <c r="G24" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H24" s="55" t="inlineStr">
+      <c r="H24" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I24" s="55" t="inlineStr">
+      <c r="I24" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J24" s="55" t="inlineStr">
+      <c r="J24" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6962,42 +8541,42 @@
           <t>Macuahuitl</t>
         </is>
       </c>
-      <c r="C25" s="55" t="inlineStr">
+      <c r="C25" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="67" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E25" s="55" t="inlineStr">
+      <c r="E25" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="55" t="inlineStr">
+      <c r="F25" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="55" t="inlineStr">
+      <c r="G25" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H25" s="55" t="inlineStr">
+      <c r="H25" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I25" s="55" t="inlineStr">
+      <c r="I25" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J25" s="55" t="inlineStr">
+      <c r="J25" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7024,42 +8603,42 @@
           <t>Pike</t>
         </is>
       </c>
-      <c r="C26" s="55" t="inlineStr">
+      <c r="C26" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E26" s="55" t="inlineStr">
+      <c r="E26" s="67" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F26" s="55" t="inlineStr">
+      <c r="F26" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="55" t="inlineStr">
+      <c r="G26" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="55" t="inlineStr">
+      <c r="H26" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I26" s="55" t="inlineStr">
+      <c r="I26" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="55" t="inlineStr">
+      <c r="J26" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7086,42 +8665,42 @@
           <t>Shortsword</t>
         </is>
       </c>
-      <c r="C27" s="55" t="inlineStr">
+      <c r="C27" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E27" s="55" t="inlineStr">
+      <c r="E27" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F27" s="55" t="inlineStr">
+      <c r="F27" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="55" t="inlineStr">
+      <c r="G27" s="67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H27" s="55" t="inlineStr">
+      <c r="H27" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I27" s="55" t="inlineStr">
+      <c r="I27" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J27" s="55" t="inlineStr">
+      <c r="J27" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7148,42 +8727,42 @@
           <t>Tomahawk</t>
         </is>
       </c>
-      <c r="C28" s="55" t="inlineStr">
+      <c r="C28" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="55" t="inlineStr">
+      <c r="E28" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="55" t="inlineStr">
+      <c r="F28" s="67" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G28" s="55" t="inlineStr">
+      <c r="G28" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="55" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I28" s="55" t="inlineStr">
+      <c r="I28" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J28" s="55" t="inlineStr">
+      <c r="J28" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7210,42 +8789,42 @@
           <t>Spear</t>
         </is>
       </c>
-      <c r="C29" s="55" t="inlineStr">
+      <c r="C29" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="55" t="inlineStr">
+      <c r="D29" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E29" s="55" t="inlineStr">
+      <c r="E29" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F29" s="55" t="inlineStr">
+      <c r="F29" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G29" s="55" t="inlineStr">
+      <c r="G29" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H29" s="55" t="inlineStr">
+      <c r="H29" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I29" s="55" t="inlineStr">
+      <c r="I29" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J29" s="55" t="inlineStr">
+      <c r="J29" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7258,6 +8837,582 @@
       <c r="L29" s="7" t="inlineStr">
         <is>
           <t>DODK compat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>Mythic CLASS</t>
+        </is>
+      </c>
+      <c r="B30" s="68" t="inlineStr"/>
+      <c r="C30" s="68" t="inlineStr"/>
+      <c r="D30" s="68" t="inlineStr"/>
+      <c r="E30" s="68" t="inlineStr"/>
+      <c r="F30" s="68" t="inlineStr"/>
+      <c r="G30" s="68" t="inlineStr"/>
+      <c r="H30" s="68" t="inlineStr"/>
+      <c r="I30" s="68" t="inlineStr"/>
+      <c r="J30" s="68" t="inlineStr"/>
+      <c r="K30" s="68" t="inlineStr"/>
+      <c r="L30" s="68" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>Baseball Bat</t>
+        </is>
+      </c>
+      <c r="C31" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" s="71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E31" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" s="71" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>BatSweep</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Unlocked via events only. +10% ATK; first hit ignores shields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B32" s="70" t="inlineStr">
+        <is>
+          <t>Trident</t>
+        </is>
+      </c>
+      <c r="C32" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" s="71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E32" s="71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F32" s="71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G32" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I32" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" s="71" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>TridentPierce</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Throwable; pierces shields; +3 ATK near naval tiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
+        <is>
+          <t>Mythic Atlatl</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E33" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G33" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H33" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I33" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>MythicAtlatl</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Upgraded Atlatl; +2 ranged/level; stuns on crit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B34" s="70" t="inlineStr">
+        <is>
+          <t>Sharps Carbine</t>
+        </is>
+      </c>
+      <c r="C34" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F34" s="71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G34" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H34" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I34" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>SharpShot</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Civil War sniper rifle; ignores 4 DEF/level; terrain cover ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>Blackbeard's Pistols</t>
+        </is>
+      </c>
+      <c r="C35" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" s="71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E35" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F35" s="71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I35" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" s="71" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>PirateVolley</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Dual pistols; fires twice per round; +5 terror morale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B36" s="70" t="inlineStr">
+        <is>
+          <t>Colt Revolver</t>
+        </is>
+      </c>
+      <c r="C36" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" s="71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G36" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" s="71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>CylinderFire</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>6-shot cylinder; no reload for 3 turns then 2-turn reload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B37" s="70" t="inlineStr">
+        <is>
+          <t>Rocket Artillery</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G37" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I37" s="71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>RocketBarrage</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Massive AoE; leaves fire modifier on tile 2 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B38" s="70" t="inlineStr">
+        <is>
+          <t>Trebuchet</t>
+        </is>
+      </c>
+      <c r="C38" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D38" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G38" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" s="71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I38" s="71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>TrebuchetLaunch</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>+50% vs Fortress; stuns defenders 1 round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="69" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="B39" s="70" t="inlineStr">
+        <is>
+          <t>Wright Flyer</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" s="71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F39" s="71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G39" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H39" s="71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I39" s="71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>AerialBombing</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Ignores all ground defense bonuses; terrifies enemy.</t>
         </is>
       </c>
     </row>
@@ -7272,7 +9427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7328,18 +9483,18 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="56" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Uniform</t>
         </is>
       </c>
-      <c r="B2" s="56" t="inlineStr"/>
-      <c r="C2" s="56" t="inlineStr"/>
-      <c r="D2" s="56" t="inlineStr"/>
-      <c r="E2" s="56" t="inlineStr"/>
-      <c r="F2" s="56" t="inlineStr"/>
-      <c r="G2" s="56" t="inlineStr"/>
-      <c r="H2" s="56" t="inlineStr"/>
+      <c r="B2" s="72" t="inlineStr"/>
+      <c r="C2" s="72" t="inlineStr"/>
+      <c r="D2" s="72" t="inlineStr"/>
+      <c r="E2" s="72" t="inlineStr"/>
+      <c r="F2" s="72" t="inlineStr"/>
+      <c r="G2" s="72" t="inlineStr"/>
+      <c r="H2" s="72" t="inlineStr"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="46" t="inlineStr">
@@ -7352,22 +9507,22 @@
           <t>Continental</t>
         </is>
       </c>
-      <c r="C3" s="57" t="inlineStr">
+      <c r="C3" s="73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D3" s="57" t="inlineStr">
+      <c r="D3" s="73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E3" s="57" t="inlineStr">
+      <c r="E3" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F3" s="57" t="inlineStr">
+      <c r="F3" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -7394,22 +9549,22 @@
           <t>Redcoat</t>
         </is>
       </c>
-      <c r="C4" s="57" t="inlineStr">
+      <c r="C4" s="73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="57" t="inlineStr">
+      <c r="D4" s="73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="57" t="inlineStr">
+      <c r="E4" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="57" t="inlineStr">
+      <c r="F4" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -7436,22 +9591,22 @@
           <t>Militia</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C5" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="57" t="inlineStr">
+      <c r="D5" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="E5" s="73" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F5" s="57" t="inlineStr">
+      <c r="F5" s="73" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -7478,22 +9633,22 @@
           <t>Light Infantry</t>
         </is>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="73" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E6" s="57" t="inlineStr">
+      <c r="E6" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F6" s="57" t="inlineStr">
+      <c r="F6" s="73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -7520,22 +9675,22 @@
           <t>Heavy Infantry</t>
         </is>
       </c>
-      <c r="C7" s="57" t="inlineStr">
+      <c r="C7" s="73" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="57" t="inlineStr">
+      <c r="E7" s="73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="57" t="inlineStr">
+      <c r="F7" s="73" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -7562,22 +9717,22 @@
           <t>Cavalry</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="73" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="57" t="inlineStr">
+      <c r="D8" s="73" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E8" s="57" t="inlineStr">
+      <c r="E8" s="73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="57" t="inlineStr">
+      <c r="F8" s="73" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -7604,22 +9759,22 @@
           <t>Artillery Corps</t>
         </is>
       </c>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="C9" s="73" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E9" s="57" t="inlineStr">
+      <c r="E9" s="73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F9" s="57" t="inlineStr">
+      <c r="F9" s="73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -7646,22 +9801,22 @@
           <t>Minuteman</t>
         </is>
       </c>
-      <c r="C10" s="57" t="inlineStr">
+      <c r="C10" s="73" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="73" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E10" s="57" t="inlineStr">
+      <c r="E10" s="73" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="57" t="inlineStr">
+      <c r="F10" s="73" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -7677,103 +9832,103 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Tombstone Cap</t>
+        </is>
+      </c>
+      <c r="C11" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E11" s="73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F11" s="73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>QuickDraw</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Frontier hat; first ranged attack each battle +5 bonus damage. FIRST DRAFT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Hardee Hat</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E12" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F12" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>HardeeDisc</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Civil War dress hat; +3 DEF/level when adjacent friendly unit present. FIRST DRAFT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Legacy</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr"/>
-      <c r="C11" s="40" t="inlineStr"/>
-      <c r="D11" s="40" t="inlineStr"/>
-      <c r="E11" s="40" t="inlineStr"/>
-      <c r="F11" s="40" t="inlineStr"/>
-      <c r="G11" s="40" t="inlineStr"/>
-      <c r="H11" s="40" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Canine</t>
-        </is>
-      </c>
-      <c r="C12" s="55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D12" s="55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E12" s="55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F12" s="55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>DODK compat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Cast</t>
-        </is>
-      </c>
-      <c r="C13" s="55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E13" s="55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F13" s="55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>DODK compat.</t>
-        </is>
-      </c>
+      <c r="B13" s="40" t="inlineStr"/>
+      <c r="C13" s="40" t="inlineStr"/>
+      <c r="D13" s="40" t="inlineStr"/>
+      <c r="E13" s="40" t="inlineStr"/>
+      <c r="F13" s="40" t="inlineStr"/>
+      <c r="G13" s="40" t="inlineStr"/>
+      <c r="H13" s="40" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
@@ -7783,37 +9938,37 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="C14" s="55" t="inlineStr">
+          <t>Canine</t>
+        </is>
+      </c>
+      <c r="C14" s="67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E14" s="55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F14" s="55" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Chain (weapon mod)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Chain mod adds to rangedOffence (inverted bug). DODK compat.</t>
+          <t>DODK compat.</t>
         </is>
       </c>
     </row>
@@ -7825,27 +9980,27 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>Archer</t>
-        </is>
-      </c>
-      <c r="C15" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D15" s="55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E15" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" s="55" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Cast</t>
+        </is>
+      </c>
+      <c r="C15" s="67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" s="67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -7867,37 +10022,37 @@
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>Plate</t>
-        </is>
-      </c>
-      <c r="C16" s="55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D16" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="55" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="C16" s="67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Chain (weapon mod)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>DODK compat.</t>
+          <t>Chain mod adds to rangedOffence (inverted bug). DODK compat.</t>
         </is>
       </c>
     </row>
@@ -7909,25 +10064,25 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>Padded</t>
-        </is>
-      </c>
-      <c r="C17" s="55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D17" s="55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E17" s="55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F17" s="55" t="inlineStr">
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7951,27 +10106,27 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Scout</t>
-        </is>
-      </c>
-      <c r="C18" s="55" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D18" s="55" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E18" s="55" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F18" s="55" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>Plate</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -7993,32 +10148,32 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C19" s="55" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D19" s="55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E19" s="55" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F19" s="55" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>Padded</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Scale (ore mod — +7 shield/level)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -8035,32 +10190,32 @@
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="C20" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" s="55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F20" s="55" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Scout</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Shell (weapon mod)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -8077,32 +10232,32 @@
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="C21" s="55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D21" s="55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E21" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" s="55" t="inlineStr">
-        <is>
-          <t>55</t>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Scale (ore mod — +7 shield/level)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -8119,32 +10274,32 @@
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>Feline</t>
-        </is>
-      </c>
-      <c r="C22" s="55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D22" s="55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E22" s="55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F22" s="55" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shell (weapon mod)</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -8161,35 +10316,119 @@
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D23" s="67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>DODK compat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Feline</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F24" s="67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>DODK compat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
           <t>Otter</t>
         </is>
       </c>
-      <c r="C23" s="55" t="inlineStr">
+      <c r="C25" s="67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D25" s="67" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E23" s="55" t="inlineStr">
+      <c r="E25" s="67" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F23" s="55" t="inlineStr">
+      <c r="F25" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>DODK compat.</t>
         </is>
@@ -8278,7 +10517,7 @@
           <t>Wetlands Fisher</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -8325,7 +10564,7 @@
           <t>Appalachian Miner</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>ENGINEER</t>
         </is>
@@ -8372,7 +10611,7 @@
           <t>Ivy League Dropout</t>
         </is>
       </c>
-      <c r="C4" s="53" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>SCHOLAR</t>
         </is>
@@ -8419,7 +10658,7 @@
           <t>Seminole Fighter</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
@@ -8466,7 +10705,7 @@
           <t>Green Mountain Farmer</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>FARMER</t>
         </is>
@@ -8513,7 +10752,7 @@
           <t>Chesapeake Shipwright</t>
         </is>
       </c>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>ENGINEER</t>
         </is>
@@ -8560,7 +10799,7 @@
           <t>Loyalist Turncoat</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -8607,7 +10846,7 @@
           <t>Tobacco Belt Drifter</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -8654,7 +10893,7 @@
           <t>War Widow</t>
         </is>
       </c>
-      <c r="C10" s="53" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
@@ -8701,7 +10940,7 @@
           <t>Indigenous Scout</t>
         </is>
       </c>
-      <c r="C11" s="53" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -8748,7 +10987,7 @@
           <t>Boston Rabble-Rouser</t>
         </is>
       </c>
-      <c r="C12" s="53" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
@@ -8795,7 +11034,7 @@
           <t>Continental Surgeon</t>
         </is>
       </c>
-      <c r="C13" s="53" t="inlineStr">
+      <c r="C13" s="65" t="inlineStr">
         <is>
           <t>HEALER</t>
         </is>
@@ -8842,7 +11081,7 @@
           <t>Nantucket Sailor</t>
         </is>
       </c>
-      <c r="C14" s="53" t="inlineStr">
+      <c r="C14" s="65" t="inlineStr">
         <is>
           <t>ADMIRAL</t>
         </is>
@@ -8889,7 +11128,7 @@
           <t>Frontier Preacher</t>
         </is>
       </c>
-      <c r="C15" s="53" t="inlineStr">
+      <c r="C15" s="65" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
@@ -8936,7 +11175,7 @@
           <t>DC Bureaucrat</t>
         </is>
       </c>
-      <c r="C16" s="53" t="inlineStr">
+      <c r="C16" s="65" t="inlineStr">
         <is>
           <t>BUREAUCRAT</t>
         </is>
@@ -8983,7 +11222,7 @@
           <t>Rust Belt Steelworker</t>
         </is>
       </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="65" t="inlineStr">
         <is>
           <t>ENGINEER</t>
         </is>
@@ -9030,7 +11269,7 @@
           <t>Plantation Deserter</t>
         </is>
       </c>
-      <c r="C18" s="53" t="inlineStr">
+      <c r="C18" s="65" t="inlineStr">
         <is>
           <t>SOLDIER</t>
         </is>
@@ -9077,7 +11316,7 @@
           <t>Swamp Witch</t>
         </is>
       </c>
-      <c r="C19" s="53" t="inlineStr">
+      <c r="C19" s="65" t="inlineStr">
         <is>
           <t>MAGE</t>
         </is>
@@ -9124,7 +11363,7 @@
           <t>Caribbean Privateer</t>
         </is>
       </c>
-      <c r="C20" s="53" t="inlineStr">
+      <c r="C20" s="65" t="inlineStr">
         <is>
           <t>ADMIRAL</t>
         </is>
@@ -9171,7 +11410,7 @@
           <t>Hawaiian Refugee</t>
         </is>
       </c>
-      <c r="C21" s="53" t="inlineStr">
+      <c r="C21" s="65" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
@@ -9218,7 +11457,7 @@
           <t>Border Mercenary</t>
         </is>
       </c>
-      <c r="C22" s="53" t="inlineStr">
+      <c r="C22" s="65" t="inlineStr">
         <is>
           <t>SOLDIER</t>
         </is>
@@ -9265,7 +11504,7 @@
           <t>Acadian Forest Ranger</t>
         </is>
       </c>
-      <c r="C23" s="53" t="inlineStr">
+      <c r="C23" s="65" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -9312,7 +11551,7 @@
           <t>Gettysburg Descendant</t>
         </is>
       </c>
-      <c r="C24" s="53" t="inlineStr">
+      <c r="C24" s="65" t="inlineStr">
         <is>
           <t>SOLDIER</t>
         </is>
@@ -9359,7 +11598,7 @@
           <t>LGBTQ+ Organizer</t>
         </is>
       </c>
-      <c r="C25" s="53" t="inlineStr">
+      <c r="C25" s="65" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
@@ -9406,7 +11645,7 @@
           <t>Carnival Barker</t>
         </is>
       </c>
-      <c r="C26" s="53" t="inlineStr">
+      <c r="C26" s="65" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
@@ -9453,7 +11692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9502,12 +11741,12 @@
       <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>Unit base stats</t>
         </is>
@@ -9525,12 +11764,12 @@
       <c r="E3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>Effect multiplier</t>
         </is>
@@ -9548,12 +11787,12 @@
       <c r="E4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>Melee penalty</t>
         </is>
@@ -9571,12 +11810,12 @@
       <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Commander morale multiplier</t>
         </is>
@@ -9609,12 +11848,12 @@
       <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="75" t="inlineStr">
         <is>
           <t>Base attack</t>
         </is>
@@ -9632,12 +11871,12 @@
       <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="74" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>Block reduction</t>
         </is>
@@ -9659,12 +11898,12 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="74" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="75" t="inlineStr">
         <is>
           <t>Shield absorption</t>
         </is>
@@ -9682,12 +11921,12 @@
       <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="75" t="inlineStr">
         <is>
           <t>Saber charge cost</t>
         </is>
@@ -9705,12 +11944,12 @@
       <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>Simultaneous counter</t>
         </is>
@@ -9739,12 +11978,12 @@
       <c r="E13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="74" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="75" t="inlineStr">
         <is>
           <t>Effective launch</t>
         </is>
@@ -9762,12 +12001,12 @@
       <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="75" t="inlineStr">
         <is>
           <t>Ranged block</t>
         </is>
@@ -9785,12 +12024,12 @@
       <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="74" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="75" t="inlineStr">
         <is>
           <t>Ranged counter</t>
         </is>
@@ -9812,12 +12051,12 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="74" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="75" t="inlineStr">
         <is>
           <t>Reload</t>
         </is>
@@ -9841,7 +12080,7 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Morale &amp; Retreat</t>
+          <t>Army Death</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -9850,14 +12089,14 @@
       <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="58" t="inlineStr">
-        <is>
-          <t>Morale &amp; Retreat</t>
-        </is>
-      </c>
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t>Retreat threshold</t>
+      <c r="A19" s="74" t="inlineStr">
+        <is>
+          <t>Army Death</t>
+        </is>
+      </c>
+      <c r="B19" s="75" t="inlineStr">
+        <is>
+          <t>Civ-style army destruction</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -9867,205 +12106,216 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Retreat triggers at manpowerInArmy / maxManpower &lt; 0.25 (25%). inRetreat = true; army loses control.</t>
+          <t>When manpowerInArmy ≤ 0 after battle, army emits signal armyDestroyed(self). country._on_army_destroyed() erases from countryArmyList, nulls tile.stationedArmy, queue_free(). No retreat system — armies die in place, instantly.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Rallying Voice mod claims to reduce this to 15% — not implemented.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="58" t="inlineStr">
-        <is>
-          <t>Morale &amp; Retreat</t>
-        </is>
-      </c>
-      <c r="B20" s="59" t="inlineStr">
-        <is>
-          <t>Army destruction</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+          <t>inRetreat/retreatTarget vars still declared on Army but no longer emitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Double Shot</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="74" t="inlineStr">
+        <is>
+          <t>Double Shot</t>
+        </is>
+      </c>
+      <c r="B21" s="75" t="inlineStr">
+        <is>
+          <t>Second volley (Double Shot T2)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>After normal ranged calculation, _army_has_siege_mod() checks for Double Shot. second_multiplier = 0.5 (50% power). Loops artillery units only. Second net applied to remaining shield then to manpower.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Only applies to artillery weapon class, not muskets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="74" t="inlineStr">
+        <is>
+          <t>Double Shot</t>
+        </is>
+      </c>
+      <c r="B22" s="75" t="inlineStr">
+        <is>
+          <t>Second volley (Double Cannonade T3)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Same as Double Shot but second_multiplier = 1.0 (full power). Additional second_bonus = artillery unit count × 3. Overrides Double Shot if both mods somehow present.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Siege</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="74" t="inlineStr">
+        <is>
+          <t>Siege</t>
+        </is>
+      </c>
+      <c r="B24" s="75" t="inlineStr">
+        <is>
+          <t>Siege score</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>armySiegeScore = unitCount × 0.1 × tile.get_siege_difficulty(). tile.get_siege_difficulty() calculates based on tile buildings.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Siege score never read in battle.gd. No siege battle type implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="74" t="inlineStr">
+        <is>
+          <t>Siege</t>
+        </is>
+      </c>
+      <c r="B25" s="75" t="inlineStr">
+        <is>
+          <t>Fortification defense</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>FIRST DRAFT</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Siege Line mod designed to bypass fortification penalties. No fortification penalty currently exists in _calculate_ranged_damage.</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Battle UI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="74" t="inlineStr">
+        <is>
+          <t>Battle UI</t>
+        </is>
+      </c>
+      <c r="B27" s="75" t="inlineStr">
+        <is>
+          <t>Projected damage display</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>deleteMode = true when manpowerInArmy ≤ 0.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>deleteMode set but no automated removal from world tile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="58" t="inlineStr">
-        <is>
-          <t>Morale &amp; Retreat</t>
-        </is>
-      </c>
-      <c r="B21" s="59" t="inlineStr">
-        <is>
-          <t>Retreat execution</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>inRetreat + retreatTarget vars declared. No pathfinding back to home tile logic exists.</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Siege</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="58" t="inlineStr">
-        <is>
-          <t>Siege</t>
-        </is>
-      </c>
-      <c r="B23" s="59" t="inlineStr">
-        <is>
-          <t>Siege score</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>armySiegeScore = unitCount × 0.1 × tile.get_siege_difficulty(). tile.get_siege_difficulty() calculates based on tile buildings.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Siege score never read in battle.gd. No siege battle type implemented.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="58" t="inlineStr">
-        <is>
-          <t>Siege</t>
-        </is>
-      </c>
-      <c r="B24" s="59" t="inlineStr">
-        <is>
-          <t>Fortification defense</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Siege Line mod designed to bypass fortification penalties. No fortification penalty currently exists in _calculate_ranged_damage.</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Battle UI shows current manpower bars and projected post-battle values for both armies before player clicks Attack.</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="74" t="inlineStr">
         <is>
           <t>Battle UI</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="B28" s="75" t="inlineStr">
+        <is>
+          <t>Reload indicator</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>In ranged mode, UI shows '(N reloading)' suffix on attacker's launch stat.</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="74" t="inlineStr">
         <is>
           <t>Battle UI</t>
         </is>
       </c>
-      <c r="B26" s="59" t="inlineStr">
-        <is>
-          <t>Projected damage display</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>Battle type display</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>FULL PASS</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Battle UI shows current manpower bars and projected post-battle values for both armies before player clicks Attack.</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="58" t="inlineStr">
-        <is>
-          <t>Battle UI</t>
-        </is>
-      </c>
-      <c r="B27" s="59" t="inlineStr">
-        <is>
-          <t>Reload indicator</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>In ranged mode, UI shows '(N reloading)' suffix on attacker's launch stat.</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="58" t="inlineStr">
-        <is>
-          <t>Battle UI</t>
-        </is>
-      </c>
-      <c r="B28" s="59" t="inlineStr">
-        <is>
-          <t>Battle type display</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>FULL PASS</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Melee shows: Shield / Punch / Block% for each side. Ranged shows: Shield / Launch / Defence% for each side.</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr"/>
+      <c r="E29" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10078,7 +12328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10116,110 +12366,110 @@
       </c>
     </row>
     <row r="2" ht="54" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="B2" s="76" t="inlineStr">
         <is>
           <t>calculateMilMods() inverted disabled check</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>unit.gd line 156</t>
+          <t>unit.gd</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Condition is `if MilMod.disabled != false` which equals `if false` (always false). NO mod effects in calculateMilMods() ever apply. Stat-boosting mods (ClubBleed, Copper, MountedCharge, etc.) are completely dead.</t>
+          <t>FIXED: Changed `if MilMod.disabled != false` to `if not MilMod.disabled`. All mod effects in calculateMilMods() now apply correctly when mods are enabled.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Change to `if MilMod.disabled == false` or `if not MilMod.disabled`.</t>
+          <t>RESOLVED — all terrain, storm, stat, and special mods now active.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="54" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>addMilMod() skips buildSelf()</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>governor.gd line 161-163</t>
+          <t>governor.gd + mil_mod.gd</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>governor.addMilMod(type, levels) creates MilMod.new() and sets only milModType. buildSelf() is commented out. All boolean flags (infantryMod, rangedMod, marineMod, entrenchMod, terrainMod, etc.) remain false on all programmatic governor mods. UI filtering and any flag-based checks will always fail.</t>
+          <t>FIXED: Added `if has_node('Sprite2D'):` guard to last 5 lines of buildSelf() so MilMod.new() instances (no scene children) can call buildSelf() safely. Uncommented `newMM.buildSelf(type)` in governor.gd addMilMod().</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Uncomment `newMM.buildSelf(type)` in addMilMod(). Note: buildSelf() accesses $Sprite2D scene children — must guard with is_inside_tree() or split data init from UI init.</t>
+          <t>RESOLVED — all governor mil mods now have proper flags set.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="62" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B4" s="61" t="inlineStr">
-        <is>
-          <t>Retreat flag set but never executed</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="B4" s="76" t="inlineStr">
+        <is>
+          <t>deleteMode + inRetreat: army not removed on death</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>army.gd calculateAttackerResults / calculateDefenderResults</t>
+          <t>army.gd + country.gd</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>inRetreat = true is set at 25% manpower. No pathfinding or movement logic acts on this flag. Army continues to accept player commands while retreating.</t>
+          <t>FIXED: Replaced deleteMode/inRetreat with `signal armyDestroyed`. Emitted when manpowerInArmy ≤ 0 in calculateAttackerResults/calculateDefenderResults. country.gd addArmy() connects signal to _on_army_destroyed() which erases from countryArmyList, nulls tile.stationedArmy, and calls queue_free().</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Implement retreat path back to homeTile; disable player control while inRetreat.</t>
+          <t>RESOLVED — Civ-style army death fully wired.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="62" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B5" s="61" t="inlineStr">
-        <is>
-          <t>deleteMode set but army not removed</t>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B5" s="76" t="inlineStr">
+        <is>
+          <t>Weapon cost matching uses legacy names only</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>army.gd calculateAttackerResults / calculateDefenderResults</t>
+          <t>army.gd surveySelf() lines 357-365</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>deleteMode = true when manpower hits 0. No code in world.gd or tile.gd removes the army from the scene tree, tile.stationedArmy, or country.countryArmyList.</t>
+          <t>The match block that calculates armyWeaponsCost uses old weapon names (Spear, Club, Atlatl etc). No case handles Cutlass, Flintlock, Field Gun, etc. New weapon armies show 0 weapons cost.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Add post-battle check in world.gd: if army.deleteMode, remove from tile and country.</t>
+          <t>Add Saber/Musket/Artillery weapon cost cases to the match block.</t>
         </is>
       </c>
     </row>
@@ -10229,24 +12479,24 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>Weapon cost matching uses legacy names only</t>
+      <c r="B6" s="76" t="inlineStr">
+        <is>
+          <t>morale vs loyalty confusion in armyPunch multiplier</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>army.gd surveySelf() lines 357-365</t>
+          <t>army.gd surveySelf() line 371</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>The match block that calculates armyWeaponsCost uses old weapon names (Spear, Club, Atlatl etc). No case handles Cutlass, Flintlock, Field Gun, etc. New weapon armies show 0 weapons cost.</t>
+          <t>Code uses `commander.morale` but governor.gd has `loyalty` (−20 to +10) and the morale var may be a separate 0-100 field not clearly initialized. If morale is always 0, the multiplier is always 1.0 (no bonus ever).</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Add Saber/Musket/Artillery weapon cost cases to the match block.</t>
+          <t>Audit governor morale initialization; confirm formula uses correct field.</t>
         </is>
       </c>
     </row>
@@ -10256,103 +12506,76 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
-        <is>
-          <t>morale vs loyalty confusion in armyPunch multiplier</t>
+      <c r="B7" s="76" t="inlineStr">
+        <is>
+          <t>commanderCheck() adds mods to units on every updateArmyUI call</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>army.gd surveySelf() line 371</t>
+          <t>army.gd commanderCheck()</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Code uses `commander.morale` but governor.gd has `loyalty` (−20 to +10) and the morale var may be a separate 0-100 field not clearly initialized. If morale is always 0, the multiplier is always 1.0 (no bonus ever).</t>
+          <t>commanderCheck() appends mods to each unit via Unit.addMilMod(MilMod) on every call. Units clear militaryModifierList in getUnitAttributes() via removeMilMod, but commanderCheck runs AFTER getUnitAttributes in the chain — units accumulate duplicate mods if updateArmyUI is called multiple times in quick succession.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Audit governor morale initialization; confirm formula uses correct field.</t>
+          <t>Verify that getUnitAttributes() fully clears militaryModifierList before commanderCheck runs. Audit the call order in updateArmyUI().</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="inlineStr">
-        <is>
-          <t>commanderCheck() adds mods to units on every updateArmyUI call</t>
+      <c r="A8" s="77" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B8" s="76" t="inlineStr">
+        <is>
+          <t>GunCrewEfficiency is the only mod that bypasses the disabled check</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>army.gd commanderCheck()</t>
+          <t>unit.gd start_reload() line 220-223</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>commanderCheck() appends mods to each unit via Unit.addMilMod(MilMod) on every call. Units clear militaryModifierList in getUnitAttributes() via removeMilMod, but commanderCheck runs AFTER getUnitAttributes in the chain — units accumulate duplicate mods if updateArmyUI is called multiple times in quick succession.</t>
+          <t>GunCrewEfficiency is checked via a separate milModType string comparison in start_reload(), bypassing the broken calculateMilMods() disabled check. This is the only mod that actually works. All other mod effects are dead until the disabled check is fixed.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Verify that getUnitAttributes() fully clears militaryModifierList before commanderCheck runs. Audit the call order in updateArmyUI().</t>
+          <t>After fixing the disabled check, ensure GunCrewEfficiency is not double-applied.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
-        <is>
-          <t>GunCrewEfficiency is the only mod that bypasses the disabled check</t>
+      <c r="B9" s="76" t="inlineStr">
+        <is>
+          <t>armyShield vs armyMaxShield display inconsistency</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>unit.gd start_reload() line 220-223</t>
+          <t>army.gd updateFinalTotals()</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>GunCrewEfficiency is checked via a separate milModType string comparison in start_reload(), bypassing the broken calculateMilMods() disabled check. This is the only mod that actually works. All other mod effects are dead until the disabled check is fixed.</t>
+          <t>updateFinalTotals() passes armyShield for both current and max values in armyCostUI3. Should pass (armyShield, armyMaxShield) to show depletion.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>After fixing the disabled check, ensure GunCrewEfficiency is not double-applied.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="63" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="inlineStr">
-        <is>
-          <t>armyShield vs armyMaxShield display inconsistency</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>army.gd updateFinalTotals()</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>updateFinalTotals() passes armyShield for both current and max values in armyCostUI3. Should pass (armyShield, armyMaxShield) to show depletion.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Change: armyCostUI3.updateSelf(armyShield, armyMaxShield)</t>
         </is>

--- a/army_masterdoc.xlsx
+++ b/army_masterdoc.xlsx
@@ -73,12 +73,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="003A1A6A"/>
+      <color rgb="001A3A00"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001A3A00"/>
+      <color rgb="003A1A6A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -93,7 +93,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="47">
     <fill>
       <patternFill/>
     </fill>
@@ -262,6 +262,46 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="005A1A7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A6A3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A5A00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="005A3A1E"/>
       </patternFill>
     </fill>
@@ -312,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -422,7 +462,10 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -436,9 +479,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -497,13 +537,61 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -515,28 +603,28 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -910,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1714,9 +1802,9 @@
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT</t>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1731,17 +1819,17 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>mil_mod.gd (marineMod flag), tile.gd (navalTileNeighbors)</t>
+          <t>mil_mod.gd (marineMod), world.gd meleePressed(), path_point_button.gd navalPathPoints</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>marineMod bool added to MilMod class. tile.navalTileNeighbors property exists on tiles. Design: if army has Marine mod, allow melee attack into adjacent naval tiles.</t>
+          <t>Army with Marine mod may melee-attack into adjacent navalPathPoints (occupied PPBs). _army_has_active_marine() checks units for enabled Marine mod. meleePressed() loops all inTile.navalPathPoints and builds melee battles on occupied ones. path_point_button.buildSelf() populates navalPathPoints from navalPathPointsEXP array. Naval Supremacy mod adds +5×unitLevel to raw_attack in _calculate_melee_damage().</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>No combat trigger checks marineMod. No UI to select naval tile as attack target. Naval Supremacy (+5 damage on Marine attacks) also pending.</t>
+          <t>PPBs must be pre-wired in editor navalPathPointsEXP. No separate naval-target UI; naval attacks triggered from same melee button as land attacks.</t>
         </is>
       </c>
     </row>
@@ -3188,6 +3276,290 @@
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Mil Mods</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>Mil Mods</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>Army Status Effect System</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>army.gd armyStatusEffects, apply_status(), _tick_status_effects()</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>armyStatusEffects: Array of dicts {type, turnsLeft, magicCostPerTurn}. apply_status(type, duration, magic_cost=0): refresh/replace existing. _tick_status_effects() on onTurnEnd: drains magic for protector buffs (self-removes at 0); DoT for Burning (5×unitCount/turn) and Diseased/Quarantined (3×/1× unitCount/turn); ticks turnsLeft and removes expired. _apply_status_effects_to_stats(): called from surveySelf(); applies all 22 debuff and 25 protector buff stat modifiers to army scores. _apply_status_flags(): sets attackBlocked, reinforcementBlocked, movement from statuses.</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>No UI widget to display active status effects on army panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="44" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Combat Status Effects</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>battle.gd _apply_combat_status_effects()</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Called from applyBattleResults() before deleteBattles signal. Rout: &gt;40% manpower lost in one battle → Routed 2 turns. Weapon-based: Baseball Bat→Shaken 1t, Trident→Terrified 2t, Mythic Atlatl→Stunned 1t, Sharps Carbine→Blinded 1t, Blackbeard's Pistols→Terrified 2t, Colt Revolver→Shaken 1t, Rocket Artillery→Burning 2t+Suppressed 1t, Trebuchet→Stunned 1t (ranged only), Wright Flyer→Suppressed 1t. Protector retaliations: Bell Witch's Harassment→Demoralize attacker 2t, Headless Terror→Terrify attacker 2t, Le Gougou's Terror→Terrify attacker 3t.</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Weapon statuses apply on every attack (no crit condition).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Mil Mods</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>Mil Mods</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>State Guard Mod System</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>mil_mod.gd, unit.gd calculateMilMods(), army.gd surveySelf()</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>26 state/provincial guard mods (Pennsylvania Guard → Bahamas Guard). Each has culturalMod=true and culturalState=state code (PA, VA, NY, etc.). Generic post-match handler in calculateMilMods(): if MilMod.culturalMod and MilMod.culturalState != '' and currentState == MilMod.culturalState: +2 attack +2 defence per level in any tile of that state. surveySelf() sets unit.currentState = inTile.tileContinent before calculateMilMods().</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>tileContinent value must match culturalState codes exactly. No gate prevents wrong-state governors from having guard mods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>Mil Mods</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>Protector Buff Casting</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>world.gd executeOutcome(), army.gd apply_status(), _tick_status_effects()</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>25 protector buff statuses (Mothman Presence, Bell Witch's Harassment, etc.) applied as army status effects via magic upkeep. executeOutcome() 'cast_protector_buff' case: tile.stationedArmy.apply_status(name, 9999, cost). turnsLeft=9999 (infinite) but drains parentCountry.TotalMagic each tick. Self-removes when magic &lt; magicCostPerTurn. _apply_status_effects_to_stats() applies buff bonuses to armyPunch/Launch/Block/Defence/Shield.</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Wiring 'cast_protector_buff' to specific event outcomes still needed per protector. No UI shows active protector buffs or magic upkeep cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="44" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
+        </is>
+      </c>
+      <c r="B92" s="29" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C92" s="30" t="inlineStr">
+        <is>
+          <t>Corruption Disease Check</t>
+        </is>
+      </c>
+      <c r="D92" s="29" t="inlineStr">
+        <is>
+          <t>army.gd onTurnEnd()</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>On each turn end: if inTile.tileCorrution &gt; 0, army has tileCorrution% chance to gain Diseased status for 2 turns. Park Ranger mod (civilianMod, toolMod) grants immunity. Disease check: randf() &lt; float(inTile.tileCorrution) / 100.0.</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Spelling 'tileCorrution' matches the in-game variable name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="44" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>FULL PASS</t>
+        </is>
+      </c>
+      <c r="B93" s="29" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C93" s="30" t="inlineStr">
+        <is>
+          <t>President + Election Season Movement</t>
+        </is>
+      </c>
+      <c r="D93" s="29" t="inlineStr">
+        <is>
+          <t>governor.gd, army.gd _commander_movement_bonus(), world.gd _grant_election_season_mods()</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Ualani Carlisle has President mod (commanderMod, +3 movement). _commander_movement_bonus() sums +3 for President and +3 for Election Season from govMilModsLvl1/2/3 arrays. Applied in onTurnEnd(): currentMovementPoints = maxMovementPoints + bonus (before _apply_status_flags() clamping). _check_election_season() calls _grant_election_season_mods() → grants Election Season to Ualani and any governor where isVicePresident = true.</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Election Season is permanent once granted. Commander must be in an army for bonus to apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="44" customHeight="1">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>Storm Status Debuffs</t>
+        </is>
+      </c>
+      <c r="D95" s="25" t="inlineStr">
+        <is>
+          <t>world.gd _apply_storm_debuffs(), _apply_storm_status_to_army()</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Applied at turn start via _on_next_turn_pressed() after _tick_storms(). Thunderstorm/Hurricane → Waterlogged 2 turns (−20% melee+ranged). Blizzard/Nor'easter → Frostbitten 2 turns (−30% melee+ranged). Fog → Blinded 1 turn (ranged halved). Tornado → Bogged Down 1t (no move) + Shaken 1t (block halved).</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Armies moving INTO storm tiles mid-turn don't get debuff until next turn start. Storm debuffs use same apply_status() refresh/replace logic.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3200,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3747,12 +4119,12 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Army may launch melee attacks into adjacent naval tile neighbors</t>
-        </is>
-      </c>
-      <c r="G16" s="34" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT — marineMod flag set; no combat trigger checks it</t>
+          <t>Army may launch melee attacks into adjacent navalPathPoints (occupied PPBs)</t>
+        </is>
+      </c>
+      <c r="G16" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — _army_has_active_marine() wired; meleePressed() loops navalPathPoints for targets</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4381,7 @@
           <t>Army may move and attack same turn without penalty</t>
         </is>
       </c>
-      <c r="G23" s="37" t="inlineStr">
+      <c r="G23" s="38" t="inlineStr">
         <is>
           <t>IDEA — no day/night cycle; movement-attack penalty doesn't exist yet</t>
         </is>
@@ -4164,20 +4536,20 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>T3 (3) MODS</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr"/>
-      <c r="C28" s="38" t="inlineStr"/>
-      <c r="D28" s="38" t="inlineStr"/>
-      <c r="E28" s="38" t="inlineStr"/>
-      <c r="F28" s="38" t="inlineStr"/>
-      <c r="G28" s="38" t="inlineStr"/>
+      <c r="B28" s="39" t="inlineStr"/>
+      <c r="C28" s="39" t="inlineStr"/>
+      <c r="D28" s="39" t="inlineStr"/>
+      <c r="E28" s="39" t="inlineStr"/>
+      <c r="F28" s="39" t="inlineStr"/>
+      <c r="G28" s="39" t="inlineStr"/>
     </row>
     <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4214,7 +4586,7 @@
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4251,7 +4623,7 @@
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4288,7 +4660,7 @@
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4318,14 +4690,14 @@
           <t>Enemy loses 10 Morale at start of each battle round</t>
         </is>
       </c>
-      <c r="G32" s="37" t="inlineStr">
+      <c r="G32" s="38" t="inlineStr">
         <is>
           <t>IDEA — no round-start morale tick in battle.gd</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="39" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4362,7 +4734,7 @@
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4399,7 +4771,7 @@
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4426,17 +4798,17 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Marine melee attacks deal +5 additional damage per level</t>
-        </is>
-      </c>
-      <c r="G35" s="34" t="inlineStr">
-        <is>
-          <t>FIRST DRAFT — requires Marine mechanic to be wired first</t>
+          <t>Marine melee attacks deal +5 additional damage per unit level</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — _army_naval_supremacy_bonus() in battle.gd adds +5×unitLevel to raw_attack in melee</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4466,14 +4838,14 @@
           <t>Army ignores enemy zone of control</t>
         </is>
       </c>
-      <c r="G36" s="37" t="inlineStr">
+      <c r="G36" s="38" t="inlineStr">
         <is>
           <t>IDEA — no ZoC system exists</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4510,7 +4882,7 @@
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4547,7 +4919,7 @@
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4584,7 +4956,7 @@
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>T3 (3)</t>
         </is>
@@ -4614,27 +4986,27 @@
           <t>+2 Movement Points; full movement usable before attacking</t>
         </is>
       </c>
-      <c r="G40" s="37" t="inlineStr">
+      <c r="G40" s="38" t="inlineStr">
         <is>
           <t>IDEA — no code reads this mod and adds to maxMovementPoints</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>Resource MODS</t>
         </is>
       </c>
-      <c r="B41" s="40" t="inlineStr"/>
-      <c r="C41" s="40" t="inlineStr"/>
-      <c r="D41" s="40" t="inlineStr"/>
-      <c r="E41" s="40" t="inlineStr"/>
-      <c r="F41" s="40" t="inlineStr"/>
-      <c r="G41" s="40" t="inlineStr"/>
+      <c r="B41" s="41" t="inlineStr"/>
+      <c r="C41" s="41" t="inlineStr"/>
+      <c r="D41" s="41" t="inlineStr"/>
+      <c r="E41" s="41" t="inlineStr"/>
+      <c r="F41" s="41" t="inlineStr"/>
+      <c r="G41" s="41" t="inlineStr"/>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="41" t="inlineStr">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4664,14 +5036,14 @@
           <t>CLUB: +2 Attack +1 Defense per level; costs Weapons</t>
         </is>
       </c>
-      <c r="G42" s="42" t="inlineStr">
+      <c r="G42" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — in calculateMilMods() but inverted disabled check prevents it firing</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4701,14 +5073,14 @@
           <t>ATLATL: +1 Attack +2 Defense per level; costs Weapons</t>
         </is>
       </c>
-      <c r="G43" s="42" t="inlineStr">
+      <c r="G43" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — in calculateMilMods() but inverted disabled check prevents it firing</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="41" t="inlineStr">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4738,14 +5110,14 @@
           <t>+1 Attack per level; costs Wood</t>
         </is>
       </c>
-      <c r="G44" s="42" t="inlineStr">
+      <c r="G44" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — in buildSelf but no case in calculateMilMods</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4775,14 +5147,14 @@
           <t>+2 Attack per level (+magic defense); costs Metal</t>
         </is>
       </c>
-      <c r="G45" s="42" t="inlineStr">
+      <c r="G45" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — Copper adds magic defense in calculateMilMods (inverted check bug)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="41" t="inlineStr">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4812,14 +5184,14 @@
           <t>+3 Attack per level; costs Metal ×3</t>
         </is>
       </c>
-      <c r="G46" s="42" t="inlineStr">
+      <c r="G46" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined in buildSelf, no case in calculateMilMods</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="41" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4849,14 +5221,14 @@
           <t>+2 Attack per level (+magic defense); costs Metal+Gold</t>
         </is>
       </c>
-      <c r="G47" s="42" t="inlineStr">
+      <c r="G47" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — Gold adds magic defense in calculateMilMods (inverted check bug)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="41" t="inlineStr">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4886,14 +5258,14 @@
           <t>+3 Attack per level; costs Metal+Magic</t>
         </is>
       </c>
-      <c r="G48" s="42" t="inlineStr">
+      <c r="G48" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined in buildSelf, no case in calculateMilMods</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="41" t="inlineStr">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
@@ -4923,7 +5295,7 @@
           <t>+3 Attack per level, −2 Harmony per level</t>
         </is>
       </c>
-      <c r="G49" s="42" t="inlineStr">
+      <c r="G49" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined in buildSelf, no case in calculateMilMods</t>
         </is>
@@ -4973,7 +5345,7 @@
           <t>+3 Attack per level, +10% speed</t>
         </is>
       </c>
-      <c r="G51" s="42" t="inlineStr">
+      <c r="G51" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined, no case in calculateMilMods; Ualani Carlisle has this</t>
         </is>
@@ -5010,7 +5382,7 @@
           <t>+1 Attack per level, +10% speed (daytime)</t>
         </is>
       </c>
-      <c r="G52" s="42" t="inlineStr">
+      <c r="G52" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined, no case in calculateMilMods; daytime check unimplemented</t>
         </is>
@@ -5047,7 +5419,7 @@
           <t>+10 reinforce rate</t>
         </is>
       </c>
-      <c r="G53" s="42" t="inlineStr">
+      <c r="G53" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined, no case in calculateMilMods; no reinforce rate modifier hooked</t>
         </is>
@@ -5084,7 +5456,7 @@
           <t>+5% Melee, +40% Ranged, +5% Spell block</t>
         </is>
       </c>
-      <c r="G54" s="42" t="inlineStr">
+      <c r="G54" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — Chain adds unitRangedOffence in calculateMilMods (inverted check bug)</t>
         </is>
@@ -5121,7 +5493,7 @@
           <t>+50% Spell block</t>
         </is>
       </c>
-      <c r="G55" s="42" t="inlineStr">
+      <c r="G55" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — defined, no direct effect in calculateMilMods</t>
         </is>
@@ -5208,7 +5580,7 @@
           <t>Bonus vs infantry morale on charge</t>
         </is>
       </c>
-      <c r="G58" s="37" t="inlineStr">
+      <c r="G58" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared, never read anywhere</t>
         </is>
@@ -5245,7 +5617,7 @@
           <t>Extra punch damage on Heavy Saber charge</t>
         </is>
       </c>
-      <c r="G59" s="37" t="inlineStr">
+      <c r="G59" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared, never read anywhere</t>
         </is>
@@ -5319,7 +5691,7 @@
           <t>Bonus when multiple musket units fire simultaneously</t>
         </is>
       </c>
-      <c r="G61" s="37" t="inlineStr">
+      <c r="G61" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared on Brown Bess, never read in battle.gd</t>
         </is>
@@ -5356,7 +5728,7 @@
           <t>Lever Repeater fires every round without reload</t>
         </is>
       </c>
-      <c r="G62" s="42" t="inlineStr">
+      <c r="G62" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — already handled by reloadTurns = 0 on weapon; mod redundant</t>
         </is>
@@ -5393,7 +5765,7 @@
           <t>Artillery ranged attack</t>
         </is>
       </c>
-      <c r="G63" s="42" t="inlineStr">
+      <c r="G63" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — all artillery can fire ranged via can_fire_ranged(); mod declared 'handled in battle.gd' but no special branch</t>
         </is>
@@ -5430,7 +5802,7 @@
           <t>Hits multiple units (Field Gun, Howitzer, Mortar)</t>
         </is>
       </c>
-      <c r="G64" s="37" t="inlineStr">
+      <c r="G64" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared, never read in battle.gd; all ranged attacks currently single-target</t>
         </is>
@@ -5467,7 +5839,7 @@
           <t>Bonus vs fortified tiles</t>
         </is>
       </c>
-      <c r="G65" s="37" t="inlineStr">
+      <c r="G65" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared on Mortar, never read in battle.gd</t>
         </is>
@@ -5554,7 +5926,7 @@
           <t>Movement not reduced by any active storm</t>
         </is>
       </c>
-      <c r="G68" s="37" t="inlineStr">
+      <c r="G68" s="38" t="inlineStr">
         <is>
           <t>IDEA — movement exemption needs army-level storm check</t>
         </is>
@@ -5591,7 +5963,7 @@
           <t>Immune to Thunderstorm morale penalty</t>
         </is>
       </c>
-      <c r="G69" s="37" t="inlineStr">
+      <c r="G69" s="38" t="inlineStr">
         <is>
           <t>IDEA — morale immunity needs army-level check</t>
         </is>
@@ -5628,7 +6000,7 @@
           <t>No movement or supply penalty in Blizzard tiles</t>
         </is>
       </c>
-      <c r="G70" s="37" t="inlineStr">
+      <c r="G70" s="38" t="inlineStr">
         <is>
           <t>IDEA — supply/movement exemption needs army-level check</t>
         </is>
@@ -5702,7 +6074,7 @@
           <t>Army ignores Tornado scatter and manpower drain</t>
         </is>
       </c>
-      <c r="G72" s="37" t="inlineStr">
+      <c r="G72" s="38" t="inlineStr">
         <is>
           <t>IDEA — Tornado scatter effect not yet implemented</t>
         </is>
@@ -5850,7 +6222,7 @@
           <t>+1 movement point in any active storm tile</t>
         </is>
       </c>
-      <c r="G76" s="37" t="inlineStr">
+      <c r="G76" s="38" t="inlineStr">
         <is>
           <t>IDEA — movement bonus needs army-level check</t>
         </is>
@@ -5887,7 +6259,7 @@
           <t>Artillery units ignore storm ranged accuracy penalty</t>
         </is>
       </c>
-      <c r="G77" s="37" t="inlineStr">
+      <c r="G77" s="38" t="inlineStr">
         <is>
           <t>IDEA — storm accuracy penalty not yet implemented</t>
         </is>
@@ -6048,7 +6420,7 @@
           <t>+5 ATK/level first 3 battle rounds. Massachusetts governors only.</t>
         </is>
       </c>
-      <c r="G82" s="37" t="inlineStr">
+      <c r="G82" s="38" t="inlineStr">
         <is>
           <t>IDEA — first-round tracking not yet in battle.gd</t>
         </is>
@@ -6196,7 +6568,7 @@
           <t>+3 ATK/level near naval tiles. New York governors only.</t>
         </is>
       </c>
-      <c r="G86" s="37" t="inlineStr">
+      <c r="G86" s="38" t="inlineStr">
         <is>
           <t>IDEA — near-naval check not in calculateMilMods yet</t>
         </is>
@@ -6307,7 +6679,7 @@
           <t>+2 movement; +2 ATK near water. Ohio governors only.</t>
         </is>
       </c>
-      <c r="G89" s="37" t="inlineStr">
+      <c r="G89" s="38" t="inlineStr">
         <is>
           <t>IDEA — movement bonus and near-water check not yet wired</t>
         </is>
@@ -6431,7 +6803,7 @@
           <t>Maps explored tiles, revealing terrain bonuses and hidden resources.</t>
         </is>
       </c>
-      <c r="G93" s="37" t="inlineStr">
+      <c r="G93" s="38" t="inlineStr">
         <is>
           <t>IDEA — reveal logic not yet wired</t>
         </is>
@@ -6468,7 +6840,7 @@
           <t>+5 manpower per turn in tile.</t>
         </is>
       </c>
-      <c r="G94" s="37" t="inlineStr">
+      <c r="G94" s="38" t="inlineStr">
         <is>
           <t>IDEA — per-turn heal not yet wired</t>
         </is>
@@ -6505,7 +6877,7 @@
           <t>Builds roads and improves structures faster.</t>
         </is>
       </c>
-      <c r="G95" s="37" t="inlineStr">
+      <c r="G95" s="38" t="inlineStr">
         <is>
           <t>IDEA — build speed modifier not yet wired</t>
         </is>
@@ -6542,7 +6914,7 @@
           <t>Reduces weapon upkeep by 1/level/turn for stationed armies.</t>
         </is>
       </c>
-      <c r="G96" s="37" t="inlineStr">
+      <c r="G96" s="38" t="inlineStr">
         <is>
           <t>IDEA — weapon cost reduction not yet wired</t>
         </is>
@@ -6579,7 +6951,7 @@
           <t>+10 manpower per turn to armies in tile.</t>
         </is>
       </c>
-      <c r="G97" s="37" t="inlineStr">
+      <c r="G97" s="38" t="inlineStr">
         <is>
           <t>IDEA — army heal not yet wired</t>
         </is>
@@ -6616,7 +6988,7 @@
           <t>+3 gold per turn.</t>
         </is>
       </c>
-      <c r="G98" s="37" t="inlineStr">
+      <c r="G98" s="38" t="inlineStr">
         <is>
           <t>IDEA — gold generation not yet wired</t>
         </is>
@@ -6653,7 +7025,7 @@
           <t>+5 loyalty/turn for tile governor.</t>
         </is>
       </c>
-      <c r="G99" s="37" t="inlineStr">
+      <c r="G99" s="38" t="inlineStr">
         <is>
           <t>IDEA — loyalty tick not yet wired</t>
         </is>
@@ -6690,7 +7062,7 @@
           <t>Reduces building costs by 15%.</t>
         </is>
       </c>
-      <c r="G100" s="37" t="inlineStr">
+      <c r="G100" s="38" t="inlineStr">
         <is>
           <t>IDEA — cost reduction not yet wired</t>
         </is>
@@ -6727,7 +7099,7 @@
           <t>+5 food per turn.</t>
         </is>
       </c>
-      <c r="G101" s="37" t="inlineStr">
+      <c r="G101" s="38" t="inlineStr">
         <is>
           <t>IDEA — food generation not yet wired</t>
         </is>
@@ -6764,7 +7136,7 @@
           <t>+3 food per turn near water tiles.</t>
         </is>
       </c>
-      <c r="G102" s="37" t="inlineStr">
+      <c r="G102" s="38" t="inlineStr">
         <is>
           <t>IDEA — water-adjacency food not yet wired</t>
         </is>
@@ -6801,7 +7173,7 @@
           <t>Reveals terrain bonuses of adjacent tiles.</t>
         </is>
       </c>
-      <c r="G103" s="37" t="inlineStr">
+      <c r="G103" s="38" t="inlineStr">
         <is>
           <t>IDEA — reveal logic not yet wired</t>
         </is>
@@ -6838,7 +7210,7 @@
           <t>+2 food +1 trade per turn.</t>
         </is>
       </c>
-      <c r="G104" s="37" t="inlineStr">
+      <c r="G104" s="38" t="inlineStr">
         <is>
           <t>IDEA — trade/food generation not yet wired</t>
         </is>
@@ -6888,7 +7260,7 @@
           <t>Continental: bonus when adjacent to other Continental units</t>
         </is>
       </c>
-      <c r="G106" s="37" t="inlineStr">
+      <c r="G106" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared on Continental armor, 'handled at army level', no army-level check</t>
         </is>
@@ -6925,7 +7297,7 @@
           <t>Redcoat: bonus to ranged when in line formation</t>
         </is>
       </c>
-      <c r="G107" s="37" t="inlineStr">
+      <c r="G107" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared on Redcoat armor, 'handled at army level', no army-level check</t>
         </is>
@@ -6962,7 +7334,7 @@
           <t>Light Infantry: can move and fire same turn</t>
         </is>
       </c>
-      <c r="G108" s="37" t="inlineStr">
+      <c r="G108" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared on Light Infantry, 'handled at army level', no movement-fire logic</t>
         </is>
@@ -6999,7 +7371,7 @@
           <t>Heavy Infantry: bonus damage on first melee attack</t>
         </is>
       </c>
-      <c r="G109" s="42" t="inlineStr">
+      <c r="G109" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — declared 'handled in battle.gd first strike bonus'; no first-round check in battle.gd</t>
         </is>
@@ -7036,7 +7408,7 @@
           <t>Cavalry: amplifies saber charge damage by 20%</t>
         </is>
       </c>
-      <c r="G110" s="42" t="inlineStr">
+      <c r="G110" s="37" t="inlineStr">
         <is>
           <t>FIRST PASS — case in calculateMilMods() adds 20% to offScore IF saber; inverted disabled check prevents firing</t>
         </is>
@@ -7110,7 +7482,7 @@
           <t>Minuteman: bonus morale in home territory</t>
         </is>
       </c>
-      <c r="G112" s="37" t="inlineStr">
+      <c r="G112" s="38" t="inlineStr">
         <is>
           <t>IDEA — declared on Minuteman, never read anywhere</t>
         </is>
@@ -7187,6 +7559,2870 @@
       <c r="G114" s="62" t="inlineStr">
         <is>
           <t>CIVILIAN — not a combat mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="63" t="inlineStr">
+        <is>
+          <t>Special MODS</t>
+        </is>
+      </c>
+      <c r="B115" s="63" t="inlineStr"/>
+      <c r="C115" s="63" t="inlineStr"/>
+      <c r="D115" s="63" t="inlineStr"/>
+      <c r="E115" s="63" t="inlineStr"/>
+      <c r="F115" s="63" t="inlineStr"/>
+      <c r="G115" s="63" t="inlineStr"/>
+    </row>
+    <row r="116" ht="36" customHeight="1">
+      <c r="A116" s="64" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B116" s="65" t="inlineStr">
+        <is>
+          <t>Civilian/Tool</t>
+        </is>
+      </c>
+      <c r="C116" s="66" t="inlineStr">
+        <is>
+          <t>Park Ranger</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>civilianMod, toolMod</t>
+        </is>
+      </c>
+      <c r="E116" s="33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>Immunity to corruption-based disease on turn end.</t>
+        </is>
+      </c>
+      <c r="G116" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — corruption disease check in army.gd onTurnEnd() skips armies whose commander has Park Ranger</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="A117" s="64" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B117" s="65" t="inlineStr">
+        <is>
+          <t>Commander/Movement</t>
+        </is>
+      </c>
+      <c r="C117" s="66" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E117" s="33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>+3 movement points per turn. Ualani Carlisle only.</t>
+        </is>
+      </c>
+      <c r="G117" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — _commander_movement_bonus() sums +3; applied before status flag clamping in onTurnEnd()</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="A118" s="64" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B118" s="65" t="inlineStr">
+        <is>
+          <t>Commander/Movement</t>
+        </is>
+      </c>
+      <c r="C118" s="66" t="inlineStr">
+        <is>
+          <t>Election Season</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E118" s="33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>+3 movement points per turn; granted to Ualani and active VP during election season.</t>
+        </is>
+      </c>
+      <c r="G118" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — _grant_election_season_mods() called by _check_election_season(); permanent once granted</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="67" t="inlineStr">
+        <is>
+          <t>State Guard MODS</t>
+        </is>
+      </c>
+      <c r="B119" s="67" t="inlineStr"/>
+      <c r="C119" s="67" t="inlineStr"/>
+      <c r="D119" s="67" t="inlineStr"/>
+      <c r="E119" s="67" t="inlineStr"/>
+      <c r="F119" s="67" t="inlineStr"/>
+      <c r="G119" s="67" t="inlineStr"/>
+    </row>
+    <row r="120" ht="36" customHeight="1">
+      <c r="A120" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B120" s="69" t="inlineStr">
+        <is>
+          <t>State/PA</t>
+        </is>
+      </c>
+      <c r="C120" s="70" t="inlineStr">
+        <is>
+          <t>Pennsylvania Guard</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E120" s="33" t="inlineStr">
+        <is>
+          <t>PA tiles</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Pennsylvania tiles</t>
+        </is>
+      </c>
+      <c r="G120" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — generic culturalMod handler in calculateMilMods(); culturalState='PA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B121" s="69" t="inlineStr">
+        <is>
+          <t>State/VA</t>
+        </is>
+      </c>
+      <c r="C121" s="70" t="inlineStr">
+        <is>
+          <t>Virginia Guard</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E121" s="33" t="inlineStr">
+        <is>
+          <t>VA tiles</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Virginia tiles</t>
+        </is>
+      </c>
+      <c r="G121" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='VA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="A122" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B122" s="69" t="inlineStr">
+        <is>
+          <t>State/NY</t>
+        </is>
+      </c>
+      <c r="C122" s="70" t="inlineStr">
+        <is>
+          <t>New York Guard</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E122" s="33" t="inlineStr">
+        <is>
+          <t>NY tiles</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in New York tiles</t>
+        </is>
+      </c>
+      <c r="G122" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='NY'</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="A123" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B123" s="69" t="inlineStr">
+        <is>
+          <t>State/MA</t>
+        </is>
+      </c>
+      <c r="C123" s="70" t="inlineStr">
+        <is>
+          <t>Massachusetts Guard</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E123" s="33" t="inlineStr">
+        <is>
+          <t>MA tiles</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Massachusetts tiles</t>
+        </is>
+      </c>
+      <c r="G123" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='MA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="36" customHeight="1">
+      <c r="A124" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B124" s="69" t="inlineStr">
+        <is>
+          <t>State/MD</t>
+        </is>
+      </c>
+      <c r="C124" s="70" t="inlineStr">
+        <is>
+          <t>Maryland Guard</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E124" s="33" t="inlineStr">
+        <is>
+          <t>MD tiles</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Maryland tiles</t>
+        </is>
+      </c>
+      <c r="G124" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='MD'</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B125" s="69" t="inlineStr">
+        <is>
+          <t>State/NC</t>
+        </is>
+      </c>
+      <c r="C125" s="70" t="inlineStr">
+        <is>
+          <t>North Carolina Guard</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E125" s="33" t="inlineStr">
+        <is>
+          <t>NC tiles</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in North Carolina tiles</t>
+        </is>
+      </c>
+      <c r="G125" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='NC'</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B126" s="69" t="inlineStr">
+        <is>
+          <t>State/SC</t>
+        </is>
+      </c>
+      <c r="C126" s="70" t="inlineStr">
+        <is>
+          <t>South Carolina Guard</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E126" s="33" t="inlineStr">
+        <is>
+          <t>SC tiles</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in South Carolina tiles</t>
+        </is>
+      </c>
+      <c r="G126" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='SC'</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B127" s="69" t="inlineStr">
+        <is>
+          <t>State/GA</t>
+        </is>
+      </c>
+      <c r="C127" s="70" t="inlineStr">
+        <is>
+          <t>Georgia Guard</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E127" s="33" t="inlineStr">
+        <is>
+          <t>GA tiles</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Georgia tiles</t>
+        </is>
+      </c>
+      <c r="G127" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='GA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B128" s="69" t="inlineStr">
+        <is>
+          <t>State/CT</t>
+        </is>
+      </c>
+      <c r="C128" s="70" t="inlineStr">
+        <is>
+          <t>Connecticut Guard</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E128" s="33" t="inlineStr">
+        <is>
+          <t>CT tiles</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Connecticut tiles</t>
+        </is>
+      </c>
+      <c r="G128" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='CT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B129" s="69" t="inlineStr">
+        <is>
+          <t>State/NJ</t>
+        </is>
+      </c>
+      <c r="C129" s="70" t="inlineStr">
+        <is>
+          <t>New Jersey Guard</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E129" s="33" t="inlineStr">
+        <is>
+          <t>NJ tiles</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in New Jersey tiles</t>
+        </is>
+      </c>
+      <c r="G129" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='NJ'</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B130" s="69" t="inlineStr">
+        <is>
+          <t>State/DE</t>
+        </is>
+      </c>
+      <c r="C130" s="70" t="inlineStr">
+        <is>
+          <t>Delaware Guard</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E130" s="33" t="inlineStr">
+        <is>
+          <t>DE tiles</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Delaware tiles</t>
+        </is>
+      </c>
+      <c r="G130" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='DE'</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B131" s="69" t="inlineStr">
+        <is>
+          <t>State/NH</t>
+        </is>
+      </c>
+      <c r="C131" s="70" t="inlineStr">
+        <is>
+          <t>New Hampshire Guard</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E131" s="33" t="inlineStr">
+        <is>
+          <t>NH tiles</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in New Hampshire tiles</t>
+        </is>
+      </c>
+      <c r="G131" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='NH'</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B132" s="69" t="inlineStr">
+        <is>
+          <t>State/RI</t>
+        </is>
+      </c>
+      <c r="C132" s="70" t="inlineStr">
+        <is>
+          <t>Rhode Island Guard</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E132" s="33" t="inlineStr">
+        <is>
+          <t>RI tiles</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Rhode Island tiles</t>
+        </is>
+      </c>
+      <c r="G132" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='RI'</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B133" s="69" t="inlineStr">
+        <is>
+          <t>State/VT</t>
+        </is>
+      </c>
+      <c r="C133" s="70" t="inlineStr">
+        <is>
+          <t>Vermont Guard</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E133" s="33" t="inlineStr">
+        <is>
+          <t>VT tiles</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Vermont tiles</t>
+        </is>
+      </c>
+      <c r="G133" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='VT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B134" s="69" t="inlineStr">
+        <is>
+          <t>State/ME</t>
+        </is>
+      </c>
+      <c r="C134" s="70" t="inlineStr">
+        <is>
+          <t>Maine Guard</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E134" s="33" t="inlineStr">
+        <is>
+          <t>ME tiles</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Maine tiles</t>
+        </is>
+      </c>
+      <c r="G134" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='ME'</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B135" s="69" t="inlineStr">
+        <is>
+          <t>State/TN</t>
+        </is>
+      </c>
+      <c r="C135" s="70" t="inlineStr">
+        <is>
+          <t>Tennessee Guard</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E135" s="33" t="inlineStr">
+        <is>
+          <t>TN tiles</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Tennessee tiles</t>
+        </is>
+      </c>
+      <c r="G135" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='TN'</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="A136" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B136" s="69" t="inlineStr">
+        <is>
+          <t>State/AL</t>
+        </is>
+      </c>
+      <c r="C136" s="70" t="inlineStr">
+        <is>
+          <t>Alabama Guard</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E136" s="33" t="inlineStr">
+        <is>
+          <t>AL tiles</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Alabama tiles</t>
+        </is>
+      </c>
+      <c r="G136" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='AL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B137" s="69" t="inlineStr">
+        <is>
+          <t>State/FL</t>
+        </is>
+      </c>
+      <c r="C137" s="70" t="inlineStr">
+        <is>
+          <t>Florida Guard</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E137" s="33" t="inlineStr">
+        <is>
+          <t>FL tiles</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Florida tiles</t>
+        </is>
+      </c>
+      <c r="G137" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='FL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B138" s="69" t="inlineStr">
+        <is>
+          <t>State/WV</t>
+        </is>
+      </c>
+      <c r="C138" s="70" t="inlineStr">
+        <is>
+          <t>West Virginia Guard</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E138" s="33" t="inlineStr">
+        <is>
+          <t>WV tiles</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in West Virginia tiles</t>
+        </is>
+      </c>
+      <c r="G138" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='WV'</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B139" s="69" t="inlineStr">
+        <is>
+          <t>State/DC</t>
+        </is>
+      </c>
+      <c r="C139" s="70" t="inlineStr">
+        <is>
+          <t>DC Guard</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E139" s="33" t="inlineStr">
+        <is>
+          <t>DC tiles</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in DC tiles</t>
+        </is>
+      </c>
+      <c r="G139" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='DC'</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="36" customHeight="1">
+      <c r="A140" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B140" s="69" t="inlineStr">
+        <is>
+          <t>Canadian/QB</t>
+        </is>
+      </c>
+      <c r="C140" s="70" t="inlineStr">
+        <is>
+          <t>Quebec Guard</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E140" s="33" t="inlineStr">
+        <is>
+          <t>CA-QB tiles</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Quebec tiles</t>
+        </is>
+      </c>
+      <c r="G140" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='CA - QB'</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="36" customHeight="1">
+      <c r="A141" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B141" s="69" t="inlineStr">
+        <is>
+          <t>Canadian/OT</t>
+        </is>
+      </c>
+      <c r="C141" s="70" t="inlineStr">
+        <is>
+          <t>Ontario Guard</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E141" s="33" t="inlineStr">
+        <is>
+          <t>CA-OT tiles</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Ontario tiles</t>
+        </is>
+      </c>
+      <c r="G141" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='CA - OT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B142" s="69" t="inlineStr">
+        <is>
+          <t>Canadian/NS</t>
+        </is>
+      </c>
+      <c r="C142" s="70" t="inlineStr">
+        <is>
+          <t>Nova Scotia Guard</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E142" s="33" t="inlineStr">
+        <is>
+          <t>CA-NS tiles</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Nova Scotia tiles</t>
+        </is>
+      </c>
+      <c r="G142" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='CA - NS'</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="36" customHeight="1">
+      <c r="A143" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B143" s="69" t="inlineStr">
+        <is>
+          <t>Canadian/NB</t>
+        </is>
+      </c>
+      <c r="C143" s="70" t="inlineStr">
+        <is>
+          <t>New Brunswick Guard</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E143" s="33" t="inlineStr">
+        <is>
+          <t>CA-NB tiles</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in New Brunswick tiles</t>
+        </is>
+      </c>
+      <c r="G143" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='CA - NB'</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B144" s="69" t="inlineStr">
+        <is>
+          <t>Canadian/PEI</t>
+        </is>
+      </c>
+      <c r="C144" s="70" t="inlineStr">
+        <is>
+          <t>Prince Edward Island Guard</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E144" s="33" t="inlineStr">
+        <is>
+          <t>CA-PEI tiles</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in PEI tiles</t>
+        </is>
+      </c>
+      <c r="G144" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='CA - PEI'</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="68" t="inlineStr">
+        <is>
+          <t>State Guard</t>
+        </is>
+      </c>
+      <c r="B145" s="69" t="inlineStr">
+        <is>
+          <t>Bahamas/BA</t>
+        </is>
+      </c>
+      <c r="C145" s="70" t="inlineStr">
+        <is>
+          <t>Bahamas Guard</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod, culturalMod</t>
+        </is>
+      </c>
+      <c r="E145" s="33" t="inlineStr">
+        <is>
+          <t>BA tiles</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>+2 Attack +2 Defence per level in Bahamas tiles</t>
+        </is>
+      </c>
+      <c r="G145" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — culturalState='BA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="71" t="inlineStr">
+        <is>
+          <t>Protector MODS</t>
+        </is>
+      </c>
+      <c r="B146" s="71" t="inlineStr"/>
+      <c r="C146" s="71" t="inlineStr"/>
+      <c r="D146" s="71" t="inlineStr"/>
+      <c r="E146" s="71" t="inlineStr"/>
+      <c r="F146" s="71" t="inlineStr"/>
+      <c r="G146" s="71" t="inlineStr"/>
+    </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="A147" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B147" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C147" s="74" t="inlineStr">
+        <is>
+          <t>Mothman Presence</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E147" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>+20 Ranged Attack, +15 Ranged Defence while active</t>
+        </is>
+      </c>
+      <c r="G147" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats(); magic upkeep in _tick_status_effects()</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="36" customHeight="1">
+      <c r="A148" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B148" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C148" s="74" t="inlineStr">
+        <is>
+          <t>Jersey Devil's Fury</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E148" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>+25 Melee Attack, +10 Ranged, +10 Block while active</t>
+        </is>
+      </c>
+      <c r="G148" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="36" customHeight="1">
+      <c r="A149" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B149" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C149" s="74" t="inlineStr">
+        <is>
+          <t>Bigfoot's Solidarity</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E149" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>+30 Block, +15 Melee Attack while active</t>
+        </is>
+      </c>
+      <c r="G149" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="36" customHeight="1">
+      <c r="A150" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B150" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C150" s="74" t="inlineStr">
+        <is>
+          <t>Thunderbird's Sovereignty</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E150" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>+25 Ranged Attack, +10 Melee Attack while active</t>
+        </is>
+      </c>
+      <c r="G150" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="36" customHeight="1">
+      <c r="A151" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B151" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C151" s="74" t="inlineStr">
+        <is>
+          <t>Headless Terror</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E151" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>+20 Attack, +10 Block; attackers become Terrified 2t while active</t>
+        </is>
+      </c>
+      <c r="G151" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — retaliation in _apply_combat_status_effects(); stat bonus in surveySelf()</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="36" customHeight="1">
+      <c r="A152" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B152" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C152" s="74" t="inlineStr">
+        <is>
+          <t>Chessie's Blessing</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E152" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>+20 Block, +15 Ranged Defence while active</t>
+        </is>
+      </c>
+      <c r="G152" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="36" customHeight="1">
+      <c r="A153" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B153" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C153" s="74" t="inlineStr">
+        <is>
+          <t>Bell Witch's Harassment</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E153" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>+15 Attack, +20 Defence; attackers become Demoralized 2t while active</t>
+        </is>
+      </c>
+      <c r="G153" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — retaliation in _apply_combat_status_effects(); stat bonus in surveySelf()</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="36" customHeight="1">
+      <c r="A154" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B154" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C154" s="74" t="inlineStr">
+        <is>
+          <t>Old Ironsides' Hull</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E154" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>+30 Shield, +20 Block while active</t>
+        </is>
+      </c>
+      <c r="G154" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="36" customHeight="1">
+      <c r="A155" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B155" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C155" s="74" t="inlineStr">
+        <is>
+          <t>Valley Forge's Will</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E155" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>+10 Attack, +25 Block, +20 Defence while active</t>
+        </is>
+      </c>
+      <c r="G155" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="36" customHeight="1">
+      <c r="A156" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B156" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C156" s="74" t="inlineStr">
+        <is>
+          <t>Snallygaster's Claim</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E156" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>+20 Attack, +10 Ranged, +10 Block while active</t>
+        </is>
+      </c>
+      <c r="G156" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="36" customHeight="1">
+      <c r="A157" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B157" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C157" s="74" t="inlineStr">
+        <is>
+          <t>Paul Revere's Ride</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E157" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>+15 Ranged, +10 Attack, +3 Movement while active</t>
+        </is>
+      </c>
+      <c r="G157" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — movement via _apply_status_flags(); stats in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="36" customHeight="1">
+      <c r="A158" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B158" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C158" s="74" t="inlineStr">
+        <is>
+          <t>Liberty Bell's Resonance</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E158" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>+25 Block, +15 Ranged Defence while active</t>
+        </is>
+      </c>
+      <c r="G158" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="36" customHeight="1">
+      <c r="A159" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B159" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C159" s="74" t="inlineStr">
+        <is>
+          <t>Green Mountain Haunting</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E159" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>+20 Block, +15 Ranged Defence while active</t>
+        </is>
+      </c>
+      <c r="G159" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="36" customHeight="1">
+      <c r="A160" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B160" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C160" s="74" t="inlineStr">
+        <is>
+          <t>Presidential Decree</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E160" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>+20 Attack, +20 Block, +15 Ranged, +15 Defence while active</t>
+        </is>
+      </c>
+      <c r="G160" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="36" customHeight="1">
+      <c r="A161" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B161" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C161" s="74" t="inlineStr">
+        <is>
+          <t>Skunk Ape's Domain</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E161" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>+20 Attack, +15 Block while active</t>
+        </is>
+      </c>
+      <c r="G161" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="36" customHeight="1">
+      <c r="A162" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B162" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C162" s="74" t="inlineStr">
+        <is>
+          <t>Eternal Vigilance</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E162" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>+25 Block, +10 Attack while active</t>
+        </is>
+      </c>
+      <c r="G162" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="36" customHeight="1">
+      <c r="A163" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B163" s="73" t="inlineStr">
+        <is>
+          <t>Protector/USA</t>
+        </is>
+      </c>
+      <c r="C163" s="74" t="inlineStr">
+        <is>
+          <t>Lincoln's Mandate</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E163" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>+15 Attack, +15 Block, +15 Ranged, +10 Defence while active</t>
+        </is>
+      </c>
+      <c r="G163" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="36" customHeight="1">
+      <c r="A164" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B164" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C164" s="74" t="inlineStr">
+        <is>
+          <t>Le Wendigo's Hunger</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E164" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>+30 Melee Attack while active</t>
+        </is>
+      </c>
+      <c r="G164" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="36" customHeight="1">
+      <c r="A165" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B165" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C165" s="74" t="inlineStr">
+        <is>
+          <t>Loup-Garou's Frenzy</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E165" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>+25 Attack, +15 Block, +10 Defence while active</t>
+        </is>
+      </c>
+      <c r="G165" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="36" customHeight="1">
+      <c r="A166" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B166" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C166" s="74" t="inlineStr">
+        <is>
+          <t>Feux Follets' Misdirection</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E166" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>+25 Ranged Defence, +15 Block while active</t>
+        </is>
+      </c>
+      <c r="G166" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="36" customHeight="1">
+      <c r="A167" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B167" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C167" s="74" t="inlineStr">
+        <is>
+          <t>Mishepeshu's Depths</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E167" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>+20 Block, +20 Ranged Defence while active</t>
+        </is>
+      </c>
+      <c r="G167" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="36" customHeight="1">
+      <c r="A168" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B168" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C168" s="74" t="inlineStr">
+        <is>
+          <t>La Corriveau's Cage</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E168" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>+20 Ranged Attack, +15 Melee Attack while active</t>
+        </is>
+      </c>
+      <c r="G168" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
+      <c r="A169" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B169" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C169" s="74" t="inlineStr">
+        <is>
+          <t>Le Carcajou's Tenacity</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E169" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>+20 Attack, +15 Block, +10 Defence while active</t>
+        </is>
+      </c>
+      <c r="G169" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — stats applied in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="36" customHeight="1">
+      <c r="A170" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B170" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C170" s="74" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E170" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>+15 Attack, +15 Ranged, +4 Movement while active</t>
+        </is>
+      </c>
+      <c r="G170" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — movement via _apply_status_flags(); stats in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="36" customHeight="1">
+      <c r="A171" s="72" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B171" s="73" t="inlineStr">
+        <is>
+          <t>Protector/CA</t>
+        </is>
+      </c>
+      <c r="C171" s="74" t="inlineStr">
+        <is>
+          <t>Le Gougou's Terror</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>commanderMod</t>
+        </is>
+      </c>
+      <c r="E171" s="33" t="inlineStr">
+        <is>
+          <t>Magic upkeep</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>+15 Attack, +20 Defence; attackers become Terrified 3t while active</t>
+        </is>
+      </c>
+      <c r="G171" s="37" t="inlineStr">
+        <is>
+          <t>FIRST PASS — retaliation in _apply_combat_status_effects(); stat bonus in surveySelf()</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="16" customHeight="1">
+      <c r="A172" s="75" t="inlineStr">
+        <is>
+          <t>Negative MODS</t>
+        </is>
+      </c>
+      <c r="B172" s="75" t="inlineStr"/>
+      <c r="C172" s="75" t="inlineStr"/>
+      <c r="D172" s="75" t="inlineStr"/>
+      <c r="E172" s="75" t="inlineStr"/>
+      <c r="F172" s="75" t="inlineStr"/>
+      <c r="G172" s="75" t="inlineStr"/>
+    </row>
+    <row r="173" ht="36" customHeight="1">
+      <c r="A173" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B173" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C173" s="78" t="inlineStr">
+        <is>
+          <t>Stunned</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E173" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>Cannot make melee attacks this turn</t>
+        </is>
+      </c>
+      <c r="G173" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — attackBlocked set in _apply_status_flags(); meleePressed() checks attackBlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="36" customHeight="1">
+      <c r="A174" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B174" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C174" s="78" t="inlineStr">
+        <is>
+          <t>Suppressed</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E174" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>Cannot fire ranged attacks this turn</t>
+        </is>
+      </c>
+      <c r="G174" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — attackBlocked set in _apply_status_flags(); rangedPressed() checks attackBlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="36" customHeight="1">
+      <c r="A175" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B175" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C175" s="78" t="inlineStr">
+        <is>
+          <t>Shaken</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E175" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>Melee block halved</t>
+        </is>
+      </c>
+      <c r="G175" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyBlock ×0.5 in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="36" customHeight="1">
+      <c r="A176" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B176" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C176" s="78" t="inlineStr">
+        <is>
+          <t>Terrified</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E176" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>Melee attack −50%, melee block −30%</t>
+        </is>
+      </c>
+      <c r="G176" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyPunch ×0.5, armyBlock ×0.7 in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="36" customHeight="1">
+      <c r="A177" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B177" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C177" s="78" t="inlineStr">
+        <is>
+          <t>Routed</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E177" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Cannot attack; melee attack zeroed; ranged defence halved</t>
+        </is>
+      </c>
+      <c r="G177" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — attackBlocked in flags; armyPunch=0, armyDefence ×0.5 in stats; triggered by &gt;40% loss in battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="36" customHeight="1">
+      <c r="A178" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B178" s="77" t="inlineStr">
+        <is>
+          <t>Negative/DoT</t>
+        </is>
+      </c>
+      <c r="C178" s="78" t="inlineStr">
+        <is>
+          <t>Burning</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E178" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Loses 5×unitCount manpower per turn (DoT)</t>
+        </is>
+      </c>
+      <c r="G178" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — DoT applied in _tick_status_effects(); triggered by Rocket Artillery weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="36" customHeight="1">
+      <c r="A179" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B179" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C179" s="78" t="inlineStr">
+        <is>
+          <t>Blinded</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E179" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>Ranged attack and ranged defence halved</t>
+        </is>
+      </c>
+      <c r="G179" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyLaunch ×0.5, armyDefence ×0.5 in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="36" customHeight="1">
+      <c r="A180" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B180" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Magic</t>
+        </is>
+      </c>
+      <c r="C180" s="78" t="inlineStr">
+        <is>
+          <t>Hexed</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E180" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>Magic defence eliminated (armyMagicDefense = 0)</t>
+        </is>
+      </c>
+      <c r="G180" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyMagicDefense=0 in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="36" customHeight="1">
+      <c r="A181" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B181" s="77" t="inlineStr">
+        <is>
+          <t>Negative/DoT</t>
+        </is>
+      </c>
+      <c r="C181" s="78" t="inlineStr">
+        <is>
+          <t>Diseased</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E181" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Loses 3×unitCount manpower per turn (DoT); caused by tile corruption chance</t>
+        </is>
+      </c>
+      <c r="G181" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — DoT in _tick_status_effects(); corruption check in onTurnEnd(); Park Ranger immunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="36" customHeight="1">
+      <c r="A182" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B182" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Storm</t>
+        </is>
+      </c>
+      <c r="C182" s="78" t="inlineStr">
+        <is>
+          <t>Waterlogged</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>isNegative, stormMod</t>
+        </is>
+      </c>
+      <c r="E182" s="33" t="inlineStr">
+        <is>
+          <t>Storm: Thunderstorm/Hurricane</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>Melee and ranged attack −20%</t>
+        </is>
+      </c>
+      <c r="G182" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — applied by _apply_storm_debuffs(); armyPunch/armyLaunch ×0.8 in stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="36" customHeight="1">
+      <c r="A183" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B183" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Storm</t>
+        </is>
+      </c>
+      <c r="C183" s="78" t="inlineStr">
+        <is>
+          <t>Frostbitten</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>isNegative, stormMod</t>
+        </is>
+      </c>
+      <c r="E183" s="33" t="inlineStr">
+        <is>
+          <t>Storm: Blizzard/Nor'easter</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Melee and ranged attack −30%</t>
+        </is>
+      </c>
+      <c r="G183" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — applied by _apply_storm_debuffs(); armyPunch/armyLaunch ×0.7 in stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="36" customHeight="1">
+      <c r="A184" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B184" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C184" s="78" t="inlineStr">
+        <is>
+          <t>Demoralized</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E184" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Melee −20%, block −20%, all mil mods disabled (calculateMilMods skipped)</t>
+        </is>
+      </c>
+      <c r="G184" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyDemoralized flag set in surveySelf(); calculateMilMods() early return if set</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="36" customHeight="1">
+      <c r="A185" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B185" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Movement</t>
+        </is>
+      </c>
+      <c r="C185" s="78" t="inlineStr">
+        <is>
+          <t>Exhausted</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E185" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Movement reduced to 1 this turn</t>
+        </is>
+      </c>
+      <c r="G185" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — currentMovementPoints clamped to max(1,val) in _apply_status_flags()</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="36" customHeight="1">
+      <c r="A186" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B186" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Movement</t>
+        </is>
+      </c>
+      <c r="C186" s="78" t="inlineStr">
+        <is>
+          <t>Bogged Down</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E186" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Cannot move this turn (movement = 0)</t>
+        </is>
+      </c>
+      <c r="G186" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — currentMovementPoints = 0 in _apply_status_flags(); triggered by Tornado storm</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="36" customHeight="1">
+      <c r="A187" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B187" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Combat</t>
+        </is>
+      </c>
+      <c r="C187" s="78" t="inlineStr">
+        <is>
+          <t>Pacified</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E187" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Cannot initiate attacks this turn</t>
+        </is>
+      </c>
+      <c r="G187" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — attackBlocked in _apply_status_flags()</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="36" customHeight="1">
+      <c r="A188" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B188" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Supply</t>
+        </is>
+      </c>
+      <c r="C188" s="78" t="inlineStr">
+        <is>
+          <t>Supply Cut</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E188" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>Cannot reinforce or resupply this turn</t>
+        </is>
+      </c>
+      <c r="G188" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — reinforcementBlocked in _apply_status_flags(); onTurnEnd() skips refill if set</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="36" customHeight="1">
+      <c r="A189" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B189" s="77" t="inlineStr">
+        <is>
+          <t>Negative/DoT</t>
+        </is>
+      </c>
+      <c r="C189" s="78" t="inlineStr">
+        <is>
+          <t>Quarantined</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E189" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>No reinforcement; loses 1×unitCount manpower per turn</t>
+        </is>
+      </c>
+      <c r="G189" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — reinforcementBlocked in flags; light DoT in _tick_status_effects()</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="36" customHeight="1">
+      <c r="A190" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B190" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Funny</t>
+        </is>
+      </c>
+      <c r="C190" s="78" t="inlineStr">
+        <is>
+          <t>Seduced</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E190" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>Commander distracted: melee zeroed; cannot attack</t>
+        </is>
+      </c>
+      <c r="G190" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyPunch=0; attackBlocked in _apply_status_effects_to_stats() / _apply_status_flags()</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="36" customHeight="1">
+      <c r="A191" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B191" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Funny</t>
+        </is>
+      </c>
+      <c r="C191" s="78" t="inlineStr">
+        <is>
+          <t>Starstruck</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E191" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>All stats −30% (armyPunch/Launch/Block/Defence ×0.7)</t>
+        </is>
+      </c>
+      <c r="G191" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — all four scores scaled in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="36" customHeight="1">
+      <c r="A192" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B192" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Funny</t>
+        </is>
+      </c>
+      <c r="C192" s="78" t="inlineStr">
+        <is>
+          <t>Hangover</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E192" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>All stats −50% (armyPunch/Launch/Block/Defence ×0.5)</t>
+        </is>
+      </c>
+      <c r="G192" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — all four scores scaled in _apply_status_effects_to_stats()</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="36" customHeight="1">
+      <c r="A193" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B193" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Funny</t>
+        </is>
+      </c>
+      <c r="C193" s="78" t="inlineStr">
+        <is>
+          <t>Love-Struck</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E193" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Melee −70%, block −70%; cannot attack</t>
+        </is>
+      </c>
+      <c r="G193" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyPunch ×0.3, armyBlock ×0.3; attackBlocked in stats/flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="36" customHeight="1">
+      <c r="A194" s="76" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B194" s="77" t="inlineStr">
+        <is>
+          <t>Negative/Funny</t>
+        </is>
+      </c>
+      <c r="C194" s="78" t="inlineStr">
+        <is>
+          <t>Mutinous</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>isNegative</t>
+        </is>
+      </c>
+      <c r="E194" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>Melee −40%; 50% chance army refuses orders each turn</t>
+        </is>
+      </c>
+      <c r="G194" s="47" t="inlineStr">
+        <is>
+          <t>FULL PASS — armyPunch ×0.6; 50% random attackBlocked in _apply_status_flags()</t>
         </is>
       </c>
     </row>
@@ -7309,42 +10545,42 @@
           <t>Cutlass</t>
         </is>
       </c>
-      <c r="C3" s="63" t="inlineStr">
+      <c r="C3" s="79" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" s="63" t="inlineStr">
+      <c r="D3" s="79" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" s="63" t="inlineStr">
+      <c r="E3" s="79" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="63" t="inlineStr">
+      <c r="F3" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" s="63" t="inlineStr">
+      <c r="G3" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="63" t="inlineStr">
+      <c r="H3" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I3" s="63" t="inlineStr">
+      <c r="I3" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="63" t="inlineStr">
+      <c r="J3" s="79" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -7371,42 +10607,42 @@
           <t>Cavalry Saber</t>
         </is>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="C4" s="79" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="D4" s="79" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="63" t="inlineStr">
+      <c r="E4" s="79" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="63" t="inlineStr">
+      <c r="F4" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="63" t="inlineStr">
+      <c r="G4" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="63" t="inlineStr">
+      <c r="H4" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="63" t="inlineStr">
+      <c r="I4" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J4" s="63" t="inlineStr">
+      <c r="J4" s="79" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -7433,42 +10669,42 @@
           <t>Light Saber</t>
         </is>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="C5" s="79" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="63" t="inlineStr">
+      <c r="D5" s="79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E5" s="63" t="inlineStr">
+      <c r="E5" s="79" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F5" s="63" t="inlineStr">
+      <c r="F5" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="63" t="inlineStr">
+      <c r="G5" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="63" t="inlineStr">
+      <c r="H5" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="63" t="inlineStr">
+      <c r="I5" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="63" t="inlineStr">
+      <c r="J5" s="79" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -7495,42 +10731,42 @@
           <t>Heavy Saber</t>
         </is>
       </c>
-      <c r="C6" s="63" t="inlineStr">
+      <c r="C6" s="79" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E6" s="63" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F6" s="63" t="inlineStr">
+      <c r="F6" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="63" t="inlineStr">
+      <c r="G6" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" s="63" t="inlineStr">
+      <c r="H6" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I6" s="63" t="inlineStr">
+      <c r="I6" s="79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J6" s="63" t="inlineStr">
+      <c r="J6" s="79" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -7547,22 +10783,22 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>Musket CLASS</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr"/>
-      <c r="C7" s="64" t="inlineStr"/>
-      <c r="D7" s="64" t="inlineStr"/>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="64" t="inlineStr"/>
-      <c r="G7" s="64" t="inlineStr"/>
-      <c r="H7" s="64" t="inlineStr"/>
-      <c r="I7" s="64" t="inlineStr"/>
-      <c r="J7" s="64" t="inlineStr"/>
-      <c r="K7" s="64" t="inlineStr"/>
-      <c r="L7" s="64" t="inlineStr"/>
+      <c r="B7" s="80" t="inlineStr"/>
+      <c r="C7" s="80" t="inlineStr"/>
+      <c r="D7" s="80" t="inlineStr"/>
+      <c r="E7" s="80" t="inlineStr"/>
+      <c r="F7" s="80" t="inlineStr"/>
+      <c r="G7" s="80" t="inlineStr"/>
+      <c r="H7" s="80" t="inlineStr"/>
+      <c r="I7" s="80" t="inlineStr"/>
+      <c r="J7" s="80" t="inlineStr"/>
+      <c r="K7" s="80" t="inlineStr"/>
+      <c r="L7" s="80" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
@@ -7575,42 +10811,42 @@
           <t>Flintlock</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E8" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F8" s="65" t="inlineStr">
+      <c r="F8" s="81" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G8" s="65" t="inlineStr">
+      <c r="G8" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H8" s="65" t="inlineStr">
+      <c r="H8" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="65" t="inlineStr">
+      <c r="I8" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J8" s="65" t="inlineStr">
+      <c r="J8" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7637,42 +10873,42 @@
           <t>Brown Bess</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F9" s="65" t="inlineStr">
+      <c r="F9" s="81" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" s="65" t="inlineStr">
+      <c r="G9" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="65" t="inlineStr">
+      <c r="H9" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" s="65" t="inlineStr">
+      <c r="I9" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J9" s="65" t="inlineStr">
+      <c r="J9" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7699,42 +10935,42 @@
           <t>Percussion Cap</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="65" t="inlineStr">
+      <c r="D10" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
+      <c r="E10" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="65" t="inlineStr">
+      <c r="F10" s="81" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G10" s="65" t="inlineStr">
+      <c r="G10" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H10" s="65" t="inlineStr">
+      <c r="H10" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="65" t="inlineStr">
+      <c r="I10" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J10" s="65" t="inlineStr">
+      <c r="J10" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7761,42 +10997,42 @@
           <t>Lever Repeater</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="65" t="inlineStr">
+      <c r="D11" s="81" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E11" s="65" t="inlineStr">
+      <c r="E11" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F11" s="65" t="inlineStr">
+      <c r="F11" s="81" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G11" s="65" t="inlineStr">
+      <c r="G11" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H11" s="65" t="inlineStr">
+      <c r="H11" s="81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I11" s="65" t="inlineStr">
+      <c r="I11" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J11" s="65" t="inlineStr">
+      <c r="J11" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7813,25 +11049,25 @@
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Artillery CLASS</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr"/>
-      <c r="C12" s="38" t="inlineStr"/>
-      <c r="D12" s="38" t="inlineStr"/>
-      <c r="E12" s="38" t="inlineStr"/>
-      <c r="F12" s="38" t="inlineStr"/>
-      <c r="G12" s="38" t="inlineStr"/>
-      <c r="H12" s="38" t="inlineStr"/>
-      <c r="I12" s="38" t="inlineStr"/>
-      <c r="J12" s="38" t="inlineStr"/>
-      <c r="K12" s="38" t="inlineStr"/>
-      <c r="L12" s="38" t="inlineStr"/>
+      <c r="B12" s="39" t="inlineStr"/>
+      <c r="C12" s="39" t="inlineStr"/>
+      <c r="D12" s="39" t="inlineStr"/>
+      <c r="E12" s="39" t="inlineStr"/>
+      <c r="F12" s="39" t="inlineStr"/>
+      <c r="G12" s="39" t="inlineStr"/>
+      <c r="H12" s="39" t="inlineStr"/>
+      <c r="I12" s="39" t="inlineStr"/>
+      <c r="J12" s="39" t="inlineStr"/>
+      <c r="K12" s="39" t="inlineStr"/>
+      <c r="L12" s="39" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Artillery</t>
         </is>
@@ -7841,42 +11077,42 @@
           <t>Falconet</t>
         </is>
       </c>
-      <c r="C13" s="66" t="inlineStr">
+      <c r="C13" s="82" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="66" t="inlineStr">
+      <c r="D13" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="66" t="inlineStr">
+      <c r="E13" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="66" t="inlineStr">
+      <c r="F13" s="82" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G13" s="66" t="inlineStr">
+      <c r="G13" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H13" s="66" t="inlineStr">
+      <c r="H13" s="82" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I13" s="66" t="inlineStr">
+      <c r="I13" s="82" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J13" s="66" t="inlineStr">
+      <c r="J13" s="82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7893,7 +11129,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Artillery</t>
         </is>
@@ -7903,42 +11139,42 @@
           <t>Field Gun</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
+      <c r="C14" s="82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="66" t="inlineStr">
+      <c r="D14" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="66" t="inlineStr">
+      <c r="E14" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="66" t="inlineStr">
+      <c r="F14" s="82" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G14" s="66" t="inlineStr">
+      <c r="G14" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="66" t="inlineStr">
+      <c r="H14" s="82" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I14" s="66" t="inlineStr">
+      <c r="I14" s="82" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J14" s="66" t="inlineStr">
+      <c r="J14" s="82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7955,7 +11191,7 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Artillery</t>
         </is>
@@ -7965,42 +11201,42 @@
           <t>Howitzer</t>
         </is>
       </c>
-      <c r="C15" s="66" t="inlineStr">
+      <c r="C15" s="82" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D15" s="66" t="inlineStr">
+      <c r="D15" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E15" s="66" t="inlineStr">
+      <c r="E15" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="66" t="inlineStr">
+      <c r="F15" s="82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G15" s="66" t="inlineStr">
+      <c r="G15" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H15" s="66" t="inlineStr">
+      <c r="H15" s="82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="66" t="inlineStr">
+      <c r="I15" s="82" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J15" s="66" t="inlineStr">
+      <c r="J15" s="82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8017,7 +11253,7 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Artillery</t>
         </is>
@@ -8027,42 +11263,42 @@
           <t>Mortar</t>
         </is>
       </c>
-      <c r="C16" s="66" t="inlineStr">
+      <c r="C16" s="82" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="66" t="inlineStr">
+      <c r="D16" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="66" t="inlineStr">
+      <c r="E16" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="66" t="inlineStr">
+      <c r="F16" s="82" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G16" s="66" t="inlineStr">
+      <c r="G16" s="82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H16" s="66" t="inlineStr">
+      <c r="H16" s="82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="66" t="inlineStr">
+      <c r="I16" s="82" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J16" s="66" t="inlineStr">
+      <c r="J16" s="82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8079,22 +11315,22 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>Legacy CLASS</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr"/>
-      <c r="C17" s="40" t="inlineStr"/>
-      <c r="D17" s="40" t="inlineStr"/>
-      <c r="E17" s="40" t="inlineStr"/>
-      <c r="F17" s="40" t="inlineStr"/>
-      <c r="G17" s="40" t="inlineStr"/>
-      <c r="H17" s="40" t="inlineStr"/>
-      <c r="I17" s="40" t="inlineStr"/>
-      <c r="J17" s="40" t="inlineStr"/>
-      <c r="K17" s="40" t="inlineStr"/>
-      <c r="L17" s="40" t="inlineStr"/>
+      <c r="B17" s="41" t="inlineStr"/>
+      <c r="C17" s="41" t="inlineStr"/>
+      <c r="D17" s="41" t="inlineStr"/>
+      <c r="E17" s="41" t="inlineStr"/>
+      <c r="F17" s="41" t="inlineStr"/>
+      <c r="G17" s="41" t="inlineStr"/>
+      <c r="H17" s="41" t="inlineStr"/>
+      <c r="I17" s="41" t="inlineStr"/>
+      <c r="J17" s="41" t="inlineStr"/>
+      <c r="K17" s="41" t="inlineStr"/>
+      <c r="L17" s="41" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
@@ -8107,42 +11343,42 @@
           <t>Atlatl</t>
         </is>
       </c>
-      <c r="C18" s="67" t="inlineStr">
+      <c r="C18" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E18" s="67" t="inlineStr">
+      <c r="E18" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="67" t="inlineStr">
+      <c r="F18" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G18" s="67" t="inlineStr">
+      <c r="G18" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H18" s="67" t="inlineStr">
+      <c r="H18" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I18" s="67" t="inlineStr">
+      <c r="I18" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J18" s="67" t="inlineStr">
+      <c r="J18" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8169,42 +11405,42 @@
           <t>Club</t>
         </is>
       </c>
-      <c r="C19" s="67" t="inlineStr">
+      <c r="C19" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="67" t="inlineStr">
+      <c r="D19" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E19" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="67" t="inlineStr">
+      <c r="F19" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G19" s="67" t="inlineStr">
+      <c r="G19" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H19" s="67" t="inlineStr">
+      <c r="H19" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I19" s="67" t="inlineStr">
+      <c r="I19" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J19" s="67" t="inlineStr">
+      <c r="J19" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8231,42 +11467,42 @@
           <t>Double Axe</t>
         </is>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="83" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="E20" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="67" t="inlineStr">
+      <c r="F20" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="67" t="inlineStr">
+      <c r="G20" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H20" s="67" t="inlineStr">
+      <c r="H20" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I20" s="67" t="inlineStr">
+      <c r="I20" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J20" s="67" t="inlineStr">
+      <c r="J20" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8293,42 +11529,42 @@
           <t>Flail</t>
         </is>
       </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C21" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="67" t="inlineStr">
+      <c r="D21" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E21" s="67" t="inlineStr">
+      <c r="E21" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F21" s="67" t="inlineStr">
+      <c r="F21" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" s="67" t="inlineStr">
+      <c r="G21" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" s="67" t="inlineStr">
+      <c r="H21" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I21" s="67" t="inlineStr">
+      <c r="I21" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J21" s="67" t="inlineStr">
+      <c r="J21" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8355,42 +11591,42 @@
           <t>Longsword</t>
         </is>
       </c>
-      <c r="C22" s="67" t="inlineStr">
+      <c r="C22" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E22" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="67" t="inlineStr">
+      <c r="F22" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="67" t="inlineStr">
+      <c r="G22" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H22" s="67" t="inlineStr">
+      <c r="H22" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I22" s="67" t="inlineStr">
+      <c r="I22" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" s="67" t="inlineStr">
+      <c r="J22" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8417,42 +11653,42 @@
           <t>Mace</t>
         </is>
       </c>
-      <c r="C23" s="67" t="inlineStr">
+      <c r="C23" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E23" s="67" t="inlineStr">
+      <c r="E23" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F23" s="67" t="inlineStr">
+      <c r="F23" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="67" t="inlineStr">
+      <c r="G23" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H23" s="67" t="inlineStr">
+      <c r="H23" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I23" s="67" t="inlineStr">
+      <c r="I23" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J23" s="67" t="inlineStr">
+      <c r="J23" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8479,42 +11715,42 @@
           <t>Machete</t>
         </is>
       </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="C24" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E24" s="67" t="inlineStr">
+      <c r="E24" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="67" t="inlineStr">
+      <c r="F24" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="67" t="inlineStr">
+      <c r="G24" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H24" s="67" t="inlineStr">
+      <c r="H24" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I24" s="67" t="inlineStr">
+      <c r="I24" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J24" s="67" t="inlineStr">
+      <c r="J24" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8541,42 +11777,42 @@
           <t>Macuahuitl</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E25" s="67" t="inlineStr">
+      <c r="E25" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="67" t="inlineStr">
+      <c r="F25" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="67" t="inlineStr">
+      <c r="G25" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H25" s="67" t="inlineStr">
+      <c r="H25" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I25" s="67" t="inlineStr">
+      <c r="I25" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J25" s="67" t="inlineStr">
+      <c r="J25" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8603,42 +11839,42 @@
           <t>Pike</t>
         </is>
       </c>
-      <c r="C26" s="67" t="inlineStr">
+      <c r="C26" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="67" t="inlineStr">
+      <c r="D26" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E26" s="67" t="inlineStr">
+      <c r="E26" s="83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F26" s="67" t="inlineStr">
+      <c r="F26" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="67" t="inlineStr">
+      <c r="G26" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="67" t="inlineStr">
+      <c r="H26" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I26" s="67" t="inlineStr">
+      <c r="I26" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="67" t="inlineStr">
+      <c r="J26" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8665,42 +11901,42 @@
           <t>Shortsword</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C27" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D27" s="67" t="inlineStr">
+      <c r="D27" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E27" s="67" t="inlineStr">
+      <c r="E27" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F27" s="67" t="inlineStr">
+      <c r="F27" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="67" t="inlineStr">
+      <c r="G27" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H27" s="67" t="inlineStr">
+      <c r="H27" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I27" s="67" t="inlineStr">
+      <c r="I27" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J27" s="67" t="inlineStr">
+      <c r="J27" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8727,42 +11963,42 @@
           <t>Tomahawk</t>
         </is>
       </c>
-      <c r="C28" s="67" t="inlineStr">
+      <c r="C28" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="67" t="inlineStr">
+      <c r="D28" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="67" t="inlineStr">
+      <c r="E28" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="67" t="inlineStr">
+      <c r="F28" s="83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G28" s="67" t="inlineStr">
+      <c r="G28" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="67" t="inlineStr">
+      <c r="H28" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I28" s="67" t="inlineStr">
+      <c r="I28" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J28" s="67" t="inlineStr">
+      <c r="J28" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8789,42 +12025,42 @@
           <t>Spear</t>
         </is>
       </c>
-      <c r="C29" s="67" t="inlineStr">
+      <c r="C29" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="67" t="inlineStr">
+      <c r="D29" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E29" s="67" t="inlineStr">
+      <c r="E29" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F29" s="67" t="inlineStr">
+      <c r="F29" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G29" s="67" t="inlineStr">
+      <c r="G29" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H29" s="67" t="inlineStr">
+      <c r="H29" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I29" s="67" t="inlineStr">
+      <c r="I29" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J29" s="67" t="inlineStr">
+      <c r="J29" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8841,70 +12077,70 @@
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="68" t="inlineStr">
+      <c r="A30" s="84" t="inlineStr">
         <is>
           <t>Mythic CLASS</t>
         </is>
       </c>
-      <c r="B30" s="68" t="inlineStr"/>
-      <c r="C30" s="68" t="inlineStr"/>
-      <c r="D30" s="68" t="inlineStr"/>
-      <c r="E30" s="68" t="inlineStr"/>
-      <c r="F30" s="68" t="inlineStr"/>
-      <c r="G30" s="68" t="inlineStr"/>
-      <c r="H30" s="68" t="inlineStr"/>
-      <c r="I30" s="68" t="inlineStr"/>
-      <c r="J30" s="68" t="inlineStr"/>
-      <c r="K30" s="68" t="inlineStr"/>
-      <c r="L30" s="68" t="inlineStr"/>
+      <c r="B30" s="84" t="inlineStr"/>
+      <c r="C30" s="84" t="inlineStr"/>
+      <c r="D30" s="84" t="inlineStr"/>
+      <c r="E30" s="84" t="inlineStr"/>
+      <c r="F30" s="84" t="inlineStr"/>
+      <c r="G30" s="84" t="inlineStr"/>
+      <c r="H30" s="84" t="inlineStr"/>
+      <c r="I30" s="84" t="inlineStr"/>
+      <c r="J30" s="84" t="inlineStr"/>
+      <c r="K30" s="84" t="inlineStr"/>
+      <c r="L30" s="84" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="69" t="inlineStr">
+      <c r="A31" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B31" s="70" t="inlineStr">
+      <c r="B31" s="86" t="inlineStr">
         <is>
           <t>Baseball Bat</t>
         </is>
       </c>
-      <c r="C31" s="71" t="inlineStr">
+      <c r="C31" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="71" t="inlineStr">
+      <c r="D31" s="87" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E31" s="71" t="inlineStr">
+      <c r="E31" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F31" s="71" t="inlineStr">
+      <c r="F31" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G31" s="71" t="inlineStr">
+      <c r="G31" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H31" s="71" t="inlineStr">
+      <c r="H31" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I31" s="71" t="inlineStr">
+      <c r="I31" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J31" s="71" t="inlineStr">
+      <c r="J31" s="87" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -8921,52 +12157,52 @@
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="69" t="inlineStr">
+      <c r="A32" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>Trident</t>
         </is>
       </c>
-      <c r="C32" s="71" t="inlineStr">
+      <c r="C32" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D32" s="71" t="inlineStr">
+      <c r="D32" s="87" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E32" s="71" t="inlineStr">
+      <c r="E32" s="87" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F32" s="71" t="inlineStr">
+      <c r="F32" s="87" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G32" s="71" t="inlineStr">
+      <c r="G32" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H32" s="71" t="inlineStr">
+      <c r="H32" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" s="71" t="inlineStr">
+      <c r="I32" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J32" s="71" t="inlineStr">
+      <c r="J32" s="87" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -8983,52 +12219,52 @@
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="69" t="inlineStr">
+      <c r="A33" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B33" s="70" t="inlineStr">
+      <c r="B33" s="86" t="inlineStr">
         <is>
           <t>Mythic Atlatl</t>
         </is>
       </c>
-      <c r="C33" s="71" t="inlineStr">
+      <c r="C33" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D33" s="71" t="inlineStr">
+      <c r="D33" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E33" s="71" t="inlineStr">
+      <c r="E33" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F33" s="71" t="inlineStr">
+      <c r="F33" s="87" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G33" s="71" t="inlineStr">
+      <c r="G33" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H33" s="71" t="inlineStr">
+      <c r="H33" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I33" s="71" t="inlineStr">
+      <c r="I33" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J33" s="71" t="inlineStr">
+      <c r="J33" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9045,52 +12281,52 @@
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="69" t="inlineStr">
+      <c r="A34" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B34" s="70" t="inlineStr">
+      <c r="B34" s="86" t="inlineStr">
         <is>
           <t>Sharps Carbine</t>
         </is>
       </c>
-      <c r="C34" s="71" t="inlineStr">
+      <c r="C34" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="71" t="inlineStr">
+      <c r="D34" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E34" s="71" t="inlineStr">
+      <c r="E34" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F34" s="71" t="inlineStr">
+      <c r="F34" s="87" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G34" s="71" t="inlineStr">
+      <c r="G34" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H34" s="71" t="inlineStr">
+      <c r="H34" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I34" s="71" t="inlineStr">
+      <c r="I34" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J34" s="71" t="inlineStr">
+      <c r="J34" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9107,52 +12343,52 @@
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="69" t="inlineStr">
+      <c r="A35" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B35" s="70" t="inlineStr">
+      <c r="B35" s="86" t="inlineStr">
         <is>
           <t>Blackbeard's Pistols</t>
         </is>
       </c>
-      <c r="C35" s="71" t="inlineStr">
+      <c r="C35" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="71" t="inlineStr">
+      <c r="D35" s="87" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E35" s="71" t="inlineStr">
+      <c r="E35" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F35" s="71" t="inlineStr">
+      <c r="F35" s="87" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G35" s="71" t="inlineStr">
+      <c r="G35" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H35" s="71" t="inlineStr">
+      <c r="H35" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I35" s="71" t="inlineStr">
+      <c r="I35" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J35" s="71" t="inlineStr">
+      <c r="J35" s="87" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -9169,52 +12405,52 @@
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="69" t="inlineStr">
+      <c r="A36" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B36" s="70" t="inlineStr">
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>Colt Revolver</t>
         </is>
       </c>
-      <c r="C36" s="71" t="inlineStr">
+      <c r="C36" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D36" s="71" t="inlineStr">
+      <c r="D36" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E36" s="71" t="inlineStr">
+      <c r="E36" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F36" s="71" t="inlineStr">
+      <c r="F36" s="87" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G36" s="71" t="inlineStr">
+      <c r="G36" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H36" s="71" t="inlineStr">
+      <c r="H36" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I36" s="71" t="inlineStr">
+      <c r="I36" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J36" s="71" t="inlineStr">
+      <c r="J36" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9231,52 +12467,52 @@
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="69" t="inlineStr">
+      <c r="A37" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B37" s="70" t="inlineStr">
+      <c r="B37" s="86" t="inlineStr">
         <is>
           <t>Rocket Artillery</t>
         </is>
       </c>
-      <c r="C37" s="71" t="inlineStr">
+      <c r="C37" s="87" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D37" s="71" t="inlineStr">
+      <c r="D37" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="71" t="inlineStr">
+      <c r="E37" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="71" t="inlineStr">
+      <c r="F37" s="87" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="G37" s="71" t="inlineStr">
+      <c r="G37" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H37" s="71" t="inlineStr">
+      <c r="H37" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I37" s="71" t="inlineStr">
+      <c r="I37" s="87" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J37" s="71" t="inlineStr">
+      <c r="J37" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9293,52 +12529,52 @@
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="69" t="inlineStr">
+      <c r="A38" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B38" s="70" t="inlineStr">
+      <c r="B38" s="86" t="inlineStr">
         <is>
           <t>Trebuchet</t>
         </is>
       </c>
-      <c r="C38" s="71" t="inlineStr">
+      <c r="C38" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D38" s="71" t="inlineStr">
+      <c r="D38" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E38" s="71" t="inlineStr">
+      <c r="E38" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F38" s="71" t="inlineStr">
+      <c r="F38" s="87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G38" s="71" t="inlineStr">
+      <c r="G38" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H38" s="71" t="inlineStr">
+      <c r="H38" s="87" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I38" s="71" t="inlineStr">
+      <c r="I38" s="87" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J38" s="71" t="inlineStr">
+      <c r="J38" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9355,52 +12591,52 @@
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="69" t="inlineStr">
+      <c r="A39" s="85" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="B39" s="70" t="inlineStr">
+      <c r="B39" s="86" t="inlineStr">
         <is>
           <t>Wright Flyer</t>
         </is>
       </c>
-      <c r="C39" s="71" t="inlineStr">
+      <c r="C39" s="87" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D39" s="71" t="inlineStr">
+      <c r="D39" s="87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E39" s="71" t="inlineStr">
+      <c r="E39" s="87" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F39" s="71" t="inlineStr">
+      <c r="F39" s="87" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G39" s="71" t="inlineStr">
+      <c r="G39" s="87" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H39" s="71" t="inlineStr">
+      <c r="H39" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I39" s="71" t="inlineStr">
+      <c r="I39" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J39" s="71" t="inlineStr">
+      <c r="J39" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9483,18 +12719,18 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>Uniform</t>
         </is>
       </c>
-      <c r="B2" s="72" t="inlineStr"/>
-      <c r="C2" s="72" t="inlineStr"/>
-      <c r="D2" s="72" t="inlineStr"/>
-      <c r="E2" s="72" t="inlineStr"/>
-      <c r="F2" s="72" t="inlineStr"/>
-      <c r="G2" s="72" t="inlineStr"/>
-      <c r="H2" s="72" t="inlineStr"/>
+      <c r="B2" s="88" t="inlineStr"/>
+      <c r="C2" s="88" t="inlineStr"/>
+      <c r="D2" s="88" t="inlineStr"/>
+      <c r="E2" s="88" t="inlineStr"/>
+      <c r="F2" s="88" t="inlineStr"/>
+      <c r="G2" s="88" t="inlineStr"/>
+      <c r="H2" s="88" t="inlineStr"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="46" t="inlineStr">
@@ -9507,22 +12743,22 @@
           <t>Continental</t>
         </is>
       </c>
-      <c r="C3" s="73" t="inlineStr">
+      <c r="C3" s="89" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D3" s="73" t="inlineStr">
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E3" s="73" t="inlineStr">
+      <c r="E3" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F3" s="73" t="inlineStr">
+      <c r="F3" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -9549,22 +12785,22 @@
           <t>Redcoat</t>
         </is>
       </c>
-      <c r="C4" s="73" t="inlineStr">
+      <c r="C4" s="89" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="73" t="inlineStr">
+      <c r="D4" s="89" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="73" t="inlineStr">
+      <c r="E4" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -9591,22 +12827,22 @@
           <t>Militia</t>
         </is>
       </c>
-      <c r="C5" s="73" t="inlineStr">
+      <c r="C5" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E5" s="73" t="inlineStr">
+      <c r="E5" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F5" s="73" t="inlineStr">
+      <c r="F5" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -9633,22 +12869,22 @@
           <t>Light Infantry</t>
         </is>
       </c>
-      <c r="C6" s="73" t="inlineStr">
+      <c r="C6" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="73" t="inlineStr">
+      <c r="D6" s="89" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E6" s="73" t="inlineStr">
+      <c r="E6" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F6" s="73" t="inlineStr">
+      <c r="F6" s="89" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -9675,22 +12911,22 @@
           <t>Heavy Infantry</t>
         </is>
       </c>
-      <c r="C7" s="73" t="inlineStr">
+      <c r="C7" s="89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="73" t="inlineStr">
+      <c r="E7" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="73" t="inlineStr">
+      <c r="F7" s="89" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -9717,22 +12953,22 @@
           <t>Cavalry</t>
         </is>
       </c>
-      <c r="C8" s="73" t="inlineStr">
+      <c r="C8" s="89" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="73" t="inlineStr">
+      <c r="D8" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E8" s="73" t="inlineStr">
+      <c r="E8" s="89" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="73" t="inlineStr">
+      <c r="F8" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -9759,22 +12995,22 @@
           <t>Artillery Corps</t>
         </is>
       </c>
-      <c r="C9" s="73" t="inlineStr">
+      <c r="C9" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D9" s="73" t="inlineStr">
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E9" s="73" t="inlineStr">
+      <c r="E9" s="89" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F9" s="73" t="inlineStr">
+      <c r="F9" s="89" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -9801,22 +13037,22 @@
           <t>Minuteman</t>
         </is>
       </c>
-      <c r="C10" s="73" t="inlineStr">
+      <c r="C10" s="89" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="73" t="inlineStr">
+      <c r="D10" s="89" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E10" s="73" t="inlineStr">
+      <c r="E10" s="89" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="73" t="inlineStr">
+      <c r="F10" s="89" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -9843,22 +13079,22 @@
           <t>Tombstone Cap</t>
         </is>
       </c>
-      <c r="C11" s="73" t="inlineStr">
+      <c r="C11" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="73" t="inlineStr">
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E11" s="73" t="inlineStr">
+      <c r="E11" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F11" s="73" t="inlineStr">
+      <c r="F11" s="89" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -9885,22 +13121,22 @@
           <t>Hardee Hat</t>
         </is>
       </c>
-      <c r="C12" s="73" t="inlineStr">
+      <c r="C12" s="89" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="73" t="inlineStr">
+      <c r="D12" s="89" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E12" s="73" t="inlineStr">
+      <c r="E12" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F12" s="73" t="inlineStr">
+      <c r="F12" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -9917,18 +13153,18 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Legacy</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr"/>
-      <c r="C13" s="40" t="inlineStr"/>
-      <c r="D13" s="40" t="inlineStr"/>
-      <c r="E13" s="40" t="inlineStr"/>
-      <c r="F13" s="40" t="inlineStr"/>
-      <c r="G13" s="40" t="inlineStr"/>
-      <c r="H13" s="40" t="inlineStr"/>
+      <c r="B13" s="41" t="inlineStr"/>
+      <c r="C13" s="41" t="inlineStr"/>
+      <c r="D13" s="41" t="inlineStr"/>
+      <c r="E13" s="41" t="inlineStr"/>
+      <c r="F13" s="41" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr"/>
+      <c r="H13" s="41" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
@@ -9941,22 +13177,22 @@
           <t>Canine</t>
         </is>
       </c>
-      <c r="C14" s="67" t="inlineStr">
+      <c r="C14" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E14" s="67" t="inlineStr">
+      <c r="E14" s="83" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F14" s="67" t="inlineStr">
+      <c r="F14" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9983,22 +13219,22 @@
           <t>Cast</t>
         </is>
       </c>
-      <c r="C15" s="67" t="inlineStr">
+      <c r="C15" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="67" t="inlineStr">
+      <c r="D15" s="83" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F15" s="67" t="inlineStr">
+      <c r="F15" s="83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -10025,22 +13261,22 @@
           <t>Chain</t>
         </is>
       </c>
-      <c r="C16" s="67" t="inlineStr">
+      <c r="C16" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="67" t="inlineStr">
+      <c r="D16" s="83" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E16" s="67" t="inlineStr">
+      <c r="E16" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F16" s="67" t="inlineStr">
+      <c r="F16" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -10067,22 +13303,22 @@
           <t>Archer</t>
         </is>
       </c>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="67" t="inlineStr">
+      <c r="D17" s="83" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E17" s="67" t="inlineStr">
+      <c r="E17" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="67" t="inlineStr">
+      <c r="F17" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10109,22 +13345,22 @@
           <t>Plate</t>
         </is>
       </c>
-      <c r="C18" s="67" t="inlineStr">
+      <c r="C18" s="83" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E18" s="67" t="inlineStr">
+      <c r="E18" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="67" t="inlineStr">
+      <c r="F18" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10151,22 +13387,22 @@
           <t>Padded</t>
         </is>
       </c>
-      <c r="C19" s="67" t="inlineStr">
+      <c r="C19" s="83" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D19" s="67" t="inlineStr">
+      <c r="D19" s="83" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E19" s="83" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F19" s="67" t="inlineStr">
+      <c r="F19" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10193,22 +13429,22 @@
           <t>Scout</t>
         </is>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="E20" s="83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F20" s="67" t="inlineStr">
+      <c r="F20" s="83" t="inlineStr">
         <is>
           <t>90</t>
         </is>
@@ -10235,22 +13471,22 @@
           <t>Scale</t>
         </is>
       </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C21" s="83" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D21" s="67" t="inlineStr">
+      <c r="D21" s="83" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E21" s="67" t="inlineStr">
+      <c r="E21" s="83" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F21" s="67" t="inlineStr">
+      <c r="F21" s="83" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -10277,22 +13513,22 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="C22" s="67" t="inlineStr">
+      <c r="C22" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E22" s="83" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F22" s="67" t="inlineStr">
+      <c r="F22" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -10319,22 +13555,22 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="C23" s="67" t="inlineStr">
+      <c r="C23" s="83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E23" s="67" t="inlineStr">
+      <c r="E23" s="83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="67" t="inlineStr">
+      <c r="F23" s="83" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -10361,22 +13597,22 @@
           <t>Feline</t>
         </is>
       </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="C24" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E24" s="67" t="inlineStr">
+      <c r="E24" s="83" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F24" s="67" t="inlineStr">
+      <c r="F24" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10403,22 +13639,22 @@
           <t>Otter</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E25" s="67" t="inlineStr">
+      <c r="E25" s="83" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F25" s="67" t="inlineStr">
+      <c r="F25" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10517,7 +13753,7 @@
           <t>Wetlands Fisher</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="81" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -10564,7 +13800,7 @@
           <t>Appalachian Miner</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="81" t="inlineStr">
         <is>
           <t>ENGINEER</t>
         </is>
@@ -10611,7 +13847,7 @@
           <t>Ivy League Dropout</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>SCHOLAR</t>
         </is>
@@ -10658,7 +13894,7 @@
           <t>Seminole Fighter</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="81" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
@@ -10705,7 +13941,7 @@
           <t>Green Mountain Farmer</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>FARMER</t>
         </is>
@@ -10752,7 +13988,7 @@
           <t>Chesapeake Shipwright</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="81" t="inlineStr">
         <is>
           <t>ENGINEER</t>
         </is>
@@ -10799,7 +14035,7 @@
           <t>Loyalist Turncoat</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -10846,7 +14082,7 @@
           <t>Tobacco Belt Drifter</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="81" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -10893,7 +14129,7 @@
           <t>War Widow</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
@@ -10940,7 +14176,7 @@
           <t>Indigenous Scout</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -10987,7 +14223,7 @@
           <t>Boston Rabble-Rouser</t>
         </is>
       </c>
-      <c r="C12" s="65" t="inlineStr">
+      <c r="C12" s="81" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
@@ -11034,7 +14270,7 @@
           <t>Continental Surgeon</t>
         </is>
       </c>
-      <c r="C13" s="65" t="inlineStr">
+      <c r="C13" s="81" t="inlineStr">
         <is>
           <t>HEALER</t>
         </is>
@@ -11081,7 +14317,7 @@
           <t>Nantucket Sailor</t>
         </is>
       </c>
-      <c r="C14" s="65" t="inlineStr">
+      <c r="C14" s="81" t="inlineStr">
         <is>
           <t>ADMIRAL</t>
         </is>
@@ -11128,7 +14364,7 @@
           <t>Frontier Preacher</t>
         </is>
       </c>
-      <c r="C15" s="65" t="inlineStr">
+      <c r="C15" s="81" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
@@ -11175,7 +14411,7 @@
           <t>DC Bureaucrat</t>
         </is>
       </c>
-      <c r="C16" s="65" t="inlineStr">
+      <c r="C16" s="81" t="inlineStr">
         <is>
           <t>BUREAUCRAT</t>
         </is>
@@ -11222,7 +14458,7 @@
           <t>Rust Belt Steelworker</t>
         </is>
       </c>
-      <c r="C17" s="65" t="inlineStr">
+      <c r="C17" s="81" t="inlineStr">
         <is>
           <t>ENGINEER</t>
         </is>
@@ -11269,7 +14505,7 @@
           <t>Plantation Deserter</t>
         </is>
       </c>
-      <c r="C18" s="65" t="inlineStr">
+      <c r="C18" s="81" t="inlineStr">
         <is>
           <t>SOLDIER</t>
         </is>
@@ -11316,7 +14552,7 @@
           <t>Swamp Witch</t>
         </is>
       </c>
-      <c r="C19" s="65" t="inlineStr">
+      <c r="C19" s="81" t="inlineStr">
         <is>
           <t>MAGE</t>
         </is>
@@ -11363,7 +14599,7 @@
           <t>Caribbean Privateer</t>
         </is>
       </c>
-      <c r="C20" s="65" t="inlineStr">
+      <c r="C20" s="81" t="inlineStr">
         <is>
           <t>ADMIRAL</t>
         </is>
@@ -11410,7 +14646,7 @@
           <t>Hawaiian Refugee</t>
         </is>
       </c>
-      <c r="C21" s="65" t="inlineStr">
+      <c r="C21" s="81" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
@@ -11457,7 +14693,7 @@
           <t>Border Mercenary</t>
         </is>
       </c>
-      <c r="C22" s="65" t="inlineStr">
+      <c r="C22" s="81" t="inlineStr">
         <is>
           <t>SOLDIER</t>
         </is>
@@ -11504,7 +14740,7 @@
           <t>Acadian Forest Ranger</t>
         </is>
       </c>
-      <c r="C23" s="65" t="inlineStr">
+      <c r="C23" s="81" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
@@ -11551,7 +14787,7 @@
           <t>Gettysburg Descendant</t>
         </is>
       </c>
-      <c r="C24" s="65" t="inlineStr">
+      <c r="C24" s="81" t="inlineStr">
         <is>
           <t>SOLDIER</t>
         </is>
@@ -11598,7 +14834,7 @@
           <t>LGBTQ+ Organizer</t>
         </is>
       </c>
-      <c r="C25" s="65" t="inlineStr">
+      <c r="C25" s="81" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
@@ -11645,7 +14881,7 @@
           <t>Carnival Barker</t>
         </is>
       </c>
-      <c r="C26" s="65" t="inlineStr">
+      <c r="C26" s="81" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
@@ -11741,12 +14977,12 @@
       <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="90" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="91" t="inlineStr">
         <is>
           <t>Unit base stats</t>
         </is>
@@ -11764,12 +15000,12 @@
       <c r="E3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="91" t="inlineStr">
         <is>
           <t>Effect multiplier</t>
         </is>
@@ -11787,12 +15023,12 @@
       <c r="E4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="91" t="inlineStr">
         <is>
           <t>Melee penalty</t>
         </is>
@@ -11810,12 +15046,12 @@
       <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="90" t="inlineStr">
         <is>
           <t>Stat Pipeline</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="91" t="inlineStr">
         <is>
           <t>Commander morale multiplier</t>
         </is>
@@ -11848,12 +15084,12 @@
       <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="90" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="91" t="inlineStr">
         <is>
           <t>Base attack</t>
         </is>
@@ -11871,12 +15107,12 @@
       <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="74" t="inlineStr">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="91" t="inlineStr">
         <is>
           <t>Block reduction</t>
         </is>
@@ -11898,12 +15134,12 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="74" t="inlineStr">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>Shield absorption</t>
         </is>
@@ -11921,12 +15157,12 @@
       <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="A11" s="90" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="91" t="inlineStr">
         <is>
           <t>Saber charge cost</t>
         </is>
@@ -11944,12 +15180,12 @@
       <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="74" t="inlineStr">
+      <c r="A12" s="90" t="inlineStr">
         <is>
           <t>Melee Round</t>
         </is>
       </c>
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="91" t="inlineStr">
         <is>
           <t>Simultaneous counter</t>
         </is>
@@ -11978,12 +15214,12 @@
       <c r="E13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="74" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B14" s="75" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
         <is>
           <t>Effective launch</t>
         </is>
@@ -12001,12 +15237,12 @@
       <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="74" t="inlineStr">
+      <c r="A15" s="90" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="91" t="inlineStr">
         <is>
           <t>Ranged block</t>
         </is>
@@ -12024,12 +15260,12 @@
       <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="74" t="inlineStr">
+      <c r="A16" s="90" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B16" s="75" t="inlineStr">
+      <c r="B16" s="91" t="inlineStr">
         <is>
           <t>Ranged counter</t>
         </is>
@@ -12051,12 +15287,12 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="74" t="inlineStr">
+      <c r="A17" s="90" t="inlineStr">
         <is>
           <t>Ranged Round</t>
         </is>
       </c>
-      <c r="B17" s="75" t="inlineStr">
+      <c r="B17" s="91" t="inlineStr">
         <is>
           <t>Reload</t>
         </is>
@@ -12089,12 +15325,12 @@
       <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="74" t="inlineStr">
+      <c r="A19" s="90" t="inlineStr">
         <is>
           <t>Army Death</t>
         </is>
       </c>
-      <c r="B19" s="75" t="inlineStr">
+      <c r="B19" s="91" t="inlineStr">
         <is>
           <t>Civ-style army destruction</t>
         </is>
@@ -12127,12 +15363,12 @@
       <c r="E20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="74" t="inlineStr">
+      <c r="A21" s="90" t="inlineStr">
         <is>
           <t>Double Shot</t>
         </is>
       </c>
-      <c r="B21" s="75" t="inlineStr">
+      <c r="B21" s="91" t="inlineStr">
         <is>
           <t>Second volley (Double Shot T2)</t>
         </is>
@@ -12154,12 +15390,12 @@
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="74" t="inlineStr">
+      <c r="A22" s="90" t="inlineStr">
         <is>
           <t>Double Shot</t>
         </is>
       </c>
-      <c r="B22" s="75" t="inlineStr">
+      <c r="B22" s="91" t="inlineStr">
         <is>
           <t>Second volley (Double Cannonade T3)</t>
         </is>
@@ -12188,12 +15424,12 @@
       <c r="E23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="74" t="inlineStr">
+      <c r="A24" s="90" t="inlineStr">
         <is>
           <t>Siege</t>
         </is>
       </c>
-      <c r="B24" s="75" t="inlineStr">
+      <c r="B24" s="91" t="inlineStr">
         <is>
           <t>Siege score</t>
         </is>
@@ -12215,12 +15451,12 @@
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="74" t="inlineStr">
+      <c r="A25" s="90" t="inlineStr">
         <is>
           <t>Siege</t>
         </is>
       </c>
-      <c r="B25" s="75" t="inlineStr">
+      <c r="B25" s="91" t="inlineStr">
         <is>
           <t>Fortification defense</t>
         </is>
@@ -12249,12 +15485,12 @@
       <c r="E26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="74" t="inlineStr">
+      <c r="A27" s="90" t="inlineStr">
         <is>
           <t>Battle UI</t>
         </is>
       </c>
-      <c r="B27" s="75" t="inlineStr">
+      <c r="B27" s="91" t="inlineStr">
         <is>
           <t>Projected damage display</t>
         </is>
@@ -12272,12 +15508,12 @@
       <c r="E27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="74" t="inlineStr">
+      <c r="A28" s="90" t="inlineStr">
         <is>
           <t>Battle UI</t>
         </is>
       </c>
-      <c r="B28" s="75" t="inlineStr">
+      <c r="B28" s="91" t="inlineStr">
         <is>
           <t>Reload indicator</t>
         </is>
@@ -12295,12 +15531,12 @@
       <c r="E28" s="7" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="74" t="inlineStr">
+      <c r="A29" s="90" t="inlineStr">
         <is>
           <t>Battle UI</t>
         </is>
       </c>
-      <c r="B29" s="75" t="inlineStr">
+      <c r="B29" s="91" t="inlineStr">
         <is>
           <t>Battle type display</t>
         </is>
@@ -12371,7 +15607,7 @@
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="B2" s="76" t="inlineStr">
+      <c r="B2" s="92" t="inlineStr">
         <is>
           <t>calculateMilMods() inverted disabled check</t>
         </is>
@@ -12398,7 +15634,7 @@
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="92" t="inlineStr">
         <is>
           <t>addMilMod() skips buildSelf()</t>
         </is>
@@ -12425,7 +15661,7 @@
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>deleteMode + inRetreat: army not removed on death</t>
         </is>
@@ -12452,7 +15688,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="92" t="inlineStr">
         <is>
           <t>Weapon cost matching uses legacy names only</t>
         </is>
@@ -12479,7 +15715,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>morale vs loyalty confusion in armyPunch multiplier</t>
         </is>
@@ -12506,7 +15742,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>commanderCheck() adds mods to units on every updateArmyUI call</t>
         </is>
@@ -12528,12 +15764,12 @@
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="92" t="inlineStr">
         <is>
           <t>GunCrewEfficiency is the only mod that bypasses the disabled check</t>
         </is>
@@ -12555,12 +15791,12 @@
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="93" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="92" t="inlineStr">
         <is>
           <t>armyShield vs armyMaxShield display inconsistency</t>
         </is>

--- a/army_masterdoc.xlsx
+++ b/army_masterdoc.xlsx
@@ -13681,7 +13681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14168,22 +14168,22 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>ARC_10</t>
+          <t>ARC_NA_01</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Indigenous Scout</t>
+          <t>Mohawk War Captain</t>
         </is>
       </c>
       <c r="C11" s="81" t="inlineStr">
         <is>
-          <t>SCOUT</t>
+          <t>WARRIOR</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Woods / Wetlands</t>
+          <t>Woods / Foothills (NY/VT/PA)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -14193,185 +14193,185 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Swamp Legs</t>
+          <t>Guerrilla Tactics</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Guerrilla Tactics</t>
+          <t>Iron Bayonet</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Ghost March</t>
+          <t>Last Stand</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>The forest is a home, not an obstacle</t>
+          <t>Held the valley when everyone else fled. Still holding.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>ARC_11</t>
+          <t>ARC_NA_02</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Boston Rabble-Rouser</t>
+          <t>Oneida Alliance Scout</t>
         </is>
       </c>
       <c r="C12" s="81" t="inlineStr">
         <is>
-          <t>ORATOR</t>
+          <t>SCOUT</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Woods / Wetlands (NY/PA/VT)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Street Tough</t>
+          <t>Woodsman</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Saber Drill</t>
+          <t>Quick Reload</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Rallying Voice</t>
+          <t>Night Raider</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Terror</t>
+          <t>Ghost March</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Their voice is a weapon; their fists the punctuation</t>
+          <t>The Alliance fractured; their loyalty to the Republic did not.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>ARC_12</t>
+          <t>ARC_NA_03</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Continental Surgeon</t>
+          <t>Wampanoag Mariner</t>
         </is>
       </c>
       <c r="C13" s="81" t="inlineStr">
         <is>
-          <t>HEALER</t>
+          <t>ADMIRAL</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Farmlands / Foothills</t>
+          <t>Wetlands (MA/RI/CT)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Steady Line</t>
+          <t>Coastal Watch</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Fortified Position</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Cleaner</t>
+          <t>Swamp Legs</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Liberator's Will</t>
+          <t>Naval Supremacy</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Saves the wounded so they can fight again tomorrow</t>
+          <t>Sailed these waters before the Pilgrims could spell the word.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="32" t="inlineStr">
         <is>
-          <t>ARC_13</t>
+          <t>ARC_NA_04</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>Lenape Guide</t>
         </is>
       </c>
       <c r="C14" s="81" t="inlineStr">
         <is>
-          <t>ADMIRAL</t>
+          <t>FARMER</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Farmlands (NY/PA/NJ)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Coastal Watch</t>
+          <t>Steady Line</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Marksman</t>
+          <t>Farmhand</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Rallying Voice</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Naval Supremacy</t>
+          <t>Continental Line</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Home is a deck; the shore is just waiting for wind</t>
+          <t>Every road through the mid-Atlantic runs through their memory.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>ARC_14</t>
+          <t>ARC_NA_05</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>Abenaki Tracker</t>
         </is>
       </c>
       <c r="C15" s="81" t="inlineStr">
         <is>
-          <t>ORATOR</t>
+          <t>SCOUT</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Woods / Foothills</t>
+          <t>Woods (ME/NH/VT/MA)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -14381,537 +14381,960 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Hill Runner</t>
+          <t>Quick Reload</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Rallying Voice</t>
+          <t>Guerrilla Tactics</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Undaunted</t>
+          <t>Ghost March</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>God and country; in that order</t>
+          <t>Three centuries of knowing which way the wind shifts.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>ARC_15</t>
+          <t>ARC_NA_06</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Cherokee Rifleman</t>
         </is>
       </c>
       <c r="C16" s="81" t="inlineStr">
         <is>
-          <t>BUREAUCRAT</t>
+          <t>SOLDIER</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Foothills (NC/TN/GA/SC)</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Fortified Position</t>
+          <t>Hill Runner</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Street Tough</t>
+          <t>Marksman</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Flanking Drill</t>
+          <t>Quick Reload</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Iron Wall</t>
+          <t>Ghost March</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Knows every regulation and which ones to ignore</t>
+          <t>Fought the British, fought the settlers, fought and fought and fought.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>ARC_16</t>
+          <t>ARC_NA_07</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Muscogee Creek Warrior</t>
         </is>
       </c>
       <c r="C17" s="81" t="inlineStr">
         <is>
-          <t>ENGINEER</t>
+          <t>WARRIOR</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Suburbs</t>
+          <t>Wetlands (AL/GA/FL)</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Powder &amp; Shot</t>
+          <t>Swamp Legs</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Fortified Position</t>
+          <t>Saber Drill</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Siege Line</t>
+          <t>Guerrilla Tactics</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Double Cannonade</t>
+          <t>Last Stand</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Built the walls, knows where they crack</t>
+          <t>The swamp is a fortress only they can navigate.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>ARC_17</t>
+          <t>ARC_NA_08</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Shawnee Runner</t>
         </is>
       </c>
       <c r="C18" s="81" t="inlineStr">
         <is>
-          <t>SOLDIER</t>
+          <t>SCOUT</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Farmlands</t>
+          <t>Woods (OH/KY/WV/PA)</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Farmhand</t>
+          <t>Woodsman</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Saber Drill</t>
+          <t>Hill Runner</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Guerrilla Tactics</t>
+          <t>Night Raider</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Last Stand</t>
+          <t>Ghost March</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Left the plantation at midnight; never looked back</t>
+          <t>No courier runs faster. No ambush comes quieter.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>ARC_18</t>
+          <t>ARC_NA_09</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Seneca War Chief</t>
         </is>
       </c>
       <c r="C19" s="81" t="inlineStr">
         <is>
-          <t>MAGE</t>
+          <t>WARRIOR</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Woods / Foothills (NY/PA)</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Swamp Legs</t>
+          <t>Woodsman</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Coastal Watch</t>
+          <t>Saber Drill</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>Cleaner</t>
+          <t>Iron Bayonet</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Terror</t>
+          <t>Entrenched</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>The bayou has its own army and she commands it</t>
+          <t>Last guardian of the western door of the Haudenosaunee.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>ARC_19</t>
+          <t>ARC_NA_10</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Catawba Rifleman</t>
         </is>
       </c>
       <c r="C20" s="81" t="inlineStr">
         <is>
-          <t>ADMIRAL</t>
+          <t>SOLDIER</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Wetlands / Suburbs</t>
+          <t>Foothills (NC/SC/VA)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Coastal Watch</t>
+          <t>Hill Runner</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Saber Drill</t>
+          <t>Marksman</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Steady Line</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Double Cannonade</t>
+          <t>Continental Line</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>No flag but profit; for now, the Republic pays better</t>
+          <t>Fought alongside Washington. Expects the debt to be remembered.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>ARC_20</t>
+          <t>ARC_11</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="C21" s="81" t="inlineStr">
         <is>
-          <t>DIPLOMAT</t>
+          <t>ORATOR</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Wetlands / Metro</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Farmhand</t>
+          <t>Street Tough</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Coastal Watch</t>
+          <t>Saber Drill</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Rallying Voice</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Naval Supremacy</t>
+          <t>Terror</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Crossed the Pacific once. The Atlantic is nothing.</t>
+          <t>Their voice is a weapon; their fists the punctuation</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="32" t="inlineStr">
         <is>
-          <t>ARC_21</t>
+          <t>ARC_12</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C22" s="81" t="inlineStr">
         <is>
-          <t>SOLDIER</t>
+          <t>HEALER</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Suburbs / Farmlands</t>
+          <t>Farmlands / Foothills</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Hill Runner</t>
+          <t>Steady Line</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Saber Drill</t>
+          <t>Fortified Position</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>Iron Bayonet</t>
+          <t>Cleaner</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Last Stand</t>
+          <t>Liberator's Will</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Fought for whoever paid; now fighting for something real</t>
+          <t>Saves the wounded so they can fight again tomorrow</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="32" t="inlineStr">
         <is>
-          <t>ARC_22</t>
+          <t>ARC_13</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C23" s="81" t="inlineStr">
         <is>
-          <t>SCOUT</t>
+          <t>ADMIRAL</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>Woods / Wetlands</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Woodsman</t>
+          <t>Coastal Watch</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Quick Reload</t>
+          <t>Marksman</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Guerrilla Tactics</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Ghost March</t>
+          <t>Naval Supremacy</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>The British burned their home; the forest remembers</t>
+          <t>Home is a deck; the shore is just waiting for wind</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="32" t="inlineStr">
         <is>
-          <t>ARC_23</t>
+          <t>ARC_14</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C24" s="81" t="inlineStr">
         <is>
-          <t>SOLDIER</t>
+          <t>ORATOR</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Farmlands / Foothills</t>
+          <t>Woods / Foothills</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Steady Line</t>
+          <t>Woodsman</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Saber Drill</t>
+          <t>Hill Runner</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Iron Bayonet</t>
+          <t>Rallying Voice</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Entrenched</t>
+          <t>Undaunted</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>A family name written in battlefield soil</t>
+          <t>God and country; in that order</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="32" t="inlineStr">
         <is>
-          <t>ARC_24</t>
+          <t>ARC_15</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C25" s="81" t="inlineStr">
         <is>
-          <t>DIPLOMAT</t>
+          <t>BUREAUCRAT</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Metro / Suburbs</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
+          <t>Fortified Position</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
           <t>Street Tough</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Steady Line</t>
-        </is>
-      </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Rallying Voice</t>
+          <t>Flanking Drill</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Continental Line</t>
+          <t>Iron Wall</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Built coalitions the old guard said were impossible</t>
+          <t>Knows every regulation and which ones to ignore</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="32" t="inlineStr">
         <is>
+          <t>ARC_16</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Rust Belt Steelworker</t>
+        </is>
+      </c>
+      <c r="C26" s="81" t="inlineStr">
+        <is>
+          <t>ENGINEER</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Suburbs</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Powder &amp; Shot</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Fortified Position</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Siege Line</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Double Cannonade</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Built the walls, knows where they crack</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>ARC_17</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Plantation Deserter</t>
+        </is>
+      </c>
+      <c r="C27" s="81" t="inlineStr">
+        <is>
+          <t>SOLDIER</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Farmhand</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Saber Drill</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Guerrilla Tactics</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Last Stand</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Left the plantation at midnight; never looked back</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>ARC_18</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Swamp Witch</t>
+        </is>
+      </c>
+      <c r="C28" s="81" t="inlineStr">
+        <is>
+          <t>MAGE</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Swamp Legs</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Coastal Watch</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Terror</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>The bayou has its own army and she commands it</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>ARC_19</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Caribbean Privateer</t>
+        </is>
+      </c>
+      <c r="C29" s="81" t="inlineStr">
+        <is>
+          <t>ADMIRAL</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands / Suburbs</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Coastal Watch</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Saber Drill</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Double Cannonade</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>No flag but profit; for now, the Republic pays better</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>ARC_20</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Hawaiian Refugee</t>
+        </is>
+      </c>
+      <c r="C30" s="81" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands / Metro</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Farmhand</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Coastal Watch</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Naval Supremacy</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Crossed the Pacific once. The Atlantic is nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>ARC_21</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Border Mercenary</t>
+        </is>
+      </c>
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>SOLDIER</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Suburbs / Farmlands</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Hill Runner</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Saber Drill</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Iron Bayonet</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Last Stand</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Fought for whoever paid; now fighting for something real</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>ARC_22</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Acadian Forest Ranger</t>
+        </is>
+      </c>
+      <c r="C32" s="81" t="inlineStr">
+        <is>
+          <t>SCOUT</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Woods / Wetlands</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Woodsman</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Quick Reload</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Guerrilla Tactics</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Ghost March</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>The British burned their home; the forest remembers</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>ARC_23</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Gettysburg Descendant</t>
+        </is>
+      </c>
+      <c r="C33" s="81" t="inlineStr">
+        <is>
+          <t>SOLDIER</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands / Foothills</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Steady Line</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Saber Drill</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Iron Bayonet</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Entrenched</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>A family name written in battlefield soil</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>ARC_24</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>LGBTQ+ Organizer</t>
+        </is>
+      </c>
+      <c r="C34" s="81" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Metro / Suburbs</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Steady Line</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Continental Line</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Built coalitions the old guard said were impossible</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
           <t>ARC_25</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Carnival Barker</t>
         </is>
       </c>
-      <c r="C26" s="81" t="inlineStr">
+      <c r="C35" s="81" t="inlineStr">
         <is>
           <t>ORATOR</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>Wetlands / Suburbs</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Street Tough</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Marksman</t>
         </is>
       </c>
-      <c r="G26" s="15" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Night Raider</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>The Long March</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>Every performance is a battle; every crowd a campaign</t>
         </is>

--- a/army_masterdoc.xlsx
+++ b/army_masterdoc.xlsx
@@ -13681,7 +13681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15337,6 +15337,1040 @@
       <c r="I35" s="6" t="inlineStr">
         <is>
           <t>Every performance is a battle; every crowd a campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>ARC_26</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Boston Irish Dockworker</t>
+        </is>
+      </c>
+      <c r="C36" s="81" t="inlineStr">
+        <is>
+          <t>SOLDIER</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>Metro (MA/NY/NJ)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Quick Reload</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Iron Bayonet</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Last Stand</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Arrived on a coffin ship and stayed to fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>ARC_27</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Cape Ann Fisherwoman</t>
+        </is>
+      </c>
+      <c r="C37" s="81" t="inlineStr">
+        <is>
+          <t>SCOUT</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands (MA/ME/NH/RI)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Coastal Watch</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Naval Supremacy</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Has been reading weather, tide, and British patrol patterns since before the war</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>ARC_28</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Yankee Tinkerer</t>
+        </is>
+      </c>
+      <c r="C38" s="81" t="inlineStr">
+        <is>
+          <t>ENGINEER</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Suburbs (MA/CT/RI/NH/VT)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Fortified Position</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Powder &amp; Shot</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Double Shot</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Double Cannonade</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Has seventeen improvements to the army's equipment and they are all correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>ARC_29</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Tammany Ward Boss</t>
+        </is>
+      </c>
+      <c r="C39" s="81" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Metro (NY/NJ)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Terror</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Controls six blocks, three polling stations, and knows where the barrels are buried</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>ARC_30</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania Dutch Braucher</t>
+        </is>
+      </c>
+      <c r="C40" s="81" t="inlineStr">
+        <is>
+          <t>HEALER</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands (PA)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Farmhand</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Corrupted Ground</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Undaunted</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Speaks the Braucherei words over the wounded and they recover faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>ARC_31</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Hudson Valley Patroon</t>
+        </is>
+      </c>
+      <c r="C41" s="81" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands (NY/NJ)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Fortified Position</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Steady Line</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Flanking Drill</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Owns the land the tenants farm and the docks the merchants use</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>ARC_32</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Scots-Irish Rifleman</t>
+        </is>
+      </c>
+      <c r="C42" s="81" t="inlineStr">
+        <is>
+          <t>SOLDIER</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Foothills (VA/WV/PA/NC/TN)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Hill Runner</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Guerrilla Tactics</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Ghost March</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Three generations in the backcountry; the long rifle is a family tradition</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>ARC_33</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Appalachian Moonshiner</t>
+        </is>
+      </c>
+      <c r="C43" s="81" t="inlineStr">
+        <is>
+          <t>SCOUT</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Foothills (WV/VA/NC/TN/PA)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Hill Runner</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Woodsman</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>Night Raider</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Ghost March</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Knows every hollow and exactly how much proof per gallon the excise men never found</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>ARC_34</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Granny Witch</t>
+        </is>
+      </c>
+      <c r="C44" s="81" t="inlineStr">
+        <is>
+          <t>MAGE</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Foothills (WV/VA/NC/TN)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Corrupted Ground</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Farmhand</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Undaunted</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Knows which plants heal, which words bind, and why the Crown's camps keep flooding</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>ARC_35</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Chesapeake Freedman Waterman</t>
+        </is>
+      </c>
+      <c r="C45" s="81" t="inlineStr">
+        <is>
+          <t>ADMIRAL</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands (MD/VA/DE)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Coastal Watch</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Swamp Legs</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Naval Supremacy</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Free Black waterman who knows the Chesapeake better than the Royal Navy</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>ARC_36</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Tidewater Gentlewoman</t>
+        </is>
+      </c>
+      <c r="C46" s="81" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands (VA/MD/NC)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Steady Line</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Continental Line</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Manages the estate, the correspondence network, and half the county's politics</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>ARC_37</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Gullah Sea Islander</t>
+        </is>
+      </c>
+      <c r="C47" s="81" t="inlineStr">
+        <is>
+          <t>WARRIOR</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands (SC/GA)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Swamp Legs</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Guerrilla Tactics</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>Night Raider</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Liberator's Will</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>The Sea Islands have their own language, their own calendar, their own war</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>ARC_38</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Underground Railroad Conductor</t>
+        </is>
+      </c>
+      <c r="C48" s="81" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands (MD/PA/DE/VA/DC)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Woodsman</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Night Raider</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Ghost March</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>The Long March</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Has moved hundreds of people north through territory the Crown claims to control</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>ARC_39</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Great Migration Church Elder</t>
+        </is>
+      </c>
+      <c r="C49" s="81" t="inlineStr">
+        <is>
+          <t>ORATOR</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>Metro (NY/PA/NJ/DC/MA)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Continental Line</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Built the congregation the same way: no help, against opposition, with permanence</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>ARC_40</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Deep South Sharecropper</t>
+        </is>
+      </c>
+      <c r="C50" s="81" t="inlineStr">
+        <is>
+          <t>FARMER</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands (SC/GA/AL/NC)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Farmhand</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Steady Line</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Flanking Drill</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Last Stand</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Has been working this land under impossible terms longer than the war has existed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>ARC_41</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Conjure Woman</t>
+        </is>
+      </c>
+      <c r="C51" s="81" t="inlineStr">
+        <is>
+          <t>MAGE</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands (SC/GA/AL/FL/NC)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Swamp Legs</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Corrupted Ground</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Night Raider</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Terror</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Hoodoo is older than the Republic and more reliable than its supply lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>ARC_42</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Florida Cracker Cowman</t>
+        </is>
+      </c>
+      <c r="C52" s="81" t="inlineStr">
+        <is>
+          <t>SCOUT</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>Farmlands (FL/GA)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Farmhand</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Hill Runner</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>Guerrilla Tactics</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Ghost March</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Riding cattle across the scrub with a whip and a long rifle</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>ARC_43</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Rust Belt Union Organizer</t>
+        </is>
+      </c>
+      <c r="C53" s="81" t="inlineStr">
+        <is>
+          <t>ORATOR</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>Suburbs (PA/NJ/NY)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>Flanking Drill</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Liberator's Will</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Has organized three factories against Crown labor requisitions and will organize a fourth</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>ARC_44</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Little Italy Neighborhood Captain</t>
+        </is>
+      </c>
+      <c r="C54" s="81" t="inlineStr">
+        <is>
+          <t>SOLDIER</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>Metro (NY/NJ/PA)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Steady Line</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>Iron Bayonet</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Iron Wall</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>The block association, the mutual aid network, and the militia are the same organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>ARC_45</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Lower East Side Organizer</t>
+        </is>
+      </c>
+      <c r="C55" s="81" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Metro (NY/NJ/PA)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Rallying Voice</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Continental Line</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>The garment workers and the radical press are already organized</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>ARC_46</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Bahamian Free Sailor</t>
+        </is>
+      </c>
+      <c r="C56" s="81" t="inlineStr">
+        <is>
+          <t>ADMIRAL</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>Wetlands (FL/BA/SC/GA)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Coastal Watch</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Swamp Legs</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Naval Supremacy</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>Runs the shallow-water routes the Royal Navy can't follow</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>ARC_47</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>DC Political Fixer</t>
+        </is>
+      </c>
+      <c r="C57" s="81" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>Metro (DC/MD/VA)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Street Tough</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Fortified Position</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>Terror</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Every leak, every loyalty question, every mandate crisis has a hand behind it</t>
         </is>
       </c>
     </row>
